--- a/www/flightdata/xlsx/eoss-393.xlsx
+++ b/www/flightdata/xlsx/eoss-393.xlsx
@@ -3870,7 +3870,7 @@
         <v>46116.30793710648</v>
       </c>
       <c r="D2" s="1">
-        <v>46116.55787037037</v>
+        <v>46116.30787037037</v>
       </c>
       <c r="E2">
         <v>5214</v>
@@ -3977,7 +3977,7 @@
         <v>46116.308000439814</v>
       </c>
       <c r="D3" s="1">
-        <v>46116.55795138889</v>
+        <v>46116.30795138889</v>
       </c>
       <c r="E3">
         <v>5214</v>
@@ -4108,7 +4108,7 @@
         <v>46116.30825469908</v>
       </c>
       <c r="D4" s="1">
-        <v>46116.558217592596</v>
+        <v>46116.308217592596</v>
       </c>
       <c r="E4">
         <v>5552</v>
@@ -4251,7 +4251,7 @@
         <v>46116.30832318287</v>
       </c>
       <c r="D5" s="1">
-        <v>46116.55829861111</v>
+        <v>46116.30829861111</v>
       </c>
       <c r="E5">
         <v>5761</v>
@@ -4394,7 +4394,7 @@
         <v>46116.30862240741</v>
       </c>
       <c r="D6" s="1">
-        <v>46116.55856481481</v>
+        <v>46116.30856481481</v>
       </c>
       <c r="E6">
         <v>6168</v>
@@ -4537,7 +4537,7 @@
         <v>46116.30869972222</v>
       </c>
       <c r="D7" s="1">
-        <v>46116.558645833335</v>
+        <v>46116.308645833335</v>
       </c>
       <c r="E7">
         <v>6367</v>
@@ -4680,7 +4680,7 @@
         <v>46116.30894137731</v>
       </c>
       <c r="D8" s="1">
-        <v>46116.558912037035</v>
+        <v>46116.308912037035</v>
       </c>
       <c r="E8">
         <v>6785</v>
@@ -4823,7 +4823,7 @@
         <v>46116.30901048611</v>
       </c>
       <c r="D9" s="1">
-        <v>46116.55899305556</v>
+        <v>46116.30899305556</v>
       </c>
       <c r="E9">
         <v>6979</v>
@@ -4966,7 +4966,7 @@
         <v>46116.30939516204</v>
       </c>
       <c r="D10" s="1">
-        <v>46116.55934027778</v>
+        <v>46116.30934027778</v>
       </c>
       <c r="E10">
         <v>7603</v>
@@ -5109,7 +5109,7 @@
         <v>46116.309635543985</v>
       </c>
       <c r="D11" s="1">
-        <v>46116.55960648148</v>
+        <v>46116.30960648148</v>
       </c>
       <c r="E11">
         <v>8065</v>
@@ -5252,7 +5252,7 @@
         <v>46116.30970527778</v>
       </c>
       <c r="D12" s="1">
-        <v>46116.5596875</v>
+        <v>46116.3096875</v>
       </c>
       <c r="E12">
         <v>8272</v>
@@ -5395,7 +5395,7 @@
         <v>46116.31001284722</v>
       </c>
       <c r="D13" s="1">
-        <v>46116.559953703705</v>
+        <v>46116.309953703705</v>
       </c>
       <c r="E13">
         <v>8773</v>
@@ -5538,7 +5538,7 @@
         <v>46116.31008178241</v>
       </c>
       <c r="D14" s="1">
-        <v>46116.56003472222</v>
+        <v>46116.31003472222</v>
       </c>
       <c r="E14">
         <v>8995</v>
@@ -5681,7 +5681,7 @@
         <v>46116.310330636574</v>
       </c>
       <c r="D15" s="1">
-        <v>46116.56030092593</v>
+        <v>46116.31030092593</v>
       </c>
       <c r="E15">
         <v>9434</v>
@@ -5824,7 +5824,7 @@
         <v>46116.31041269676</v>
       </c>
       <c r="D16" s="1">
-        <v>46116.560381944444</v>
+        <v>46116.310381944444</v>
       </c>
       <c r="E16">
         <v>9641</v>
@@ -5967,7 +5967,7 @@
         <v>46116.310706157405</v>
       </c>
       <c r="D17" s="1">
-        <v>46116.560648148145</v>
+        <v>46116.310648148145</v>
       </c>
       <c r="E17">
         <v>10130</v>
@@ -6110,7 +6110,7 @@
         <v>46116.310775729165</v>
       </c>
       <c r="D18" s="1">
-        <v>46116.56072916667</v>
+        <v>46116.31072916667</v>
       </c>
       <c r="E18">
         <v>10338</v>
@@ -6253,7 +6253,7 @@
         <v>46116.31102454861</v>
       </c>
       <c r="D19" s="1">
-        <v>46116.56099537037</v>
+        <v>46116.31099537037</v>
       </c>
       <c r="E19">
         <v>10776</v>
@@ -6396,7 +6396,7 @@
         <v>46116.31109456019</v>
       </c>
       <c r="D20" s="1">
-        <v>46116.56107638889</v>
+        <v>46116.31107638889</v>
       </c>
       <c r="E20">
         <v>10979</v>
@@ -6539,7 +6539,7 @@
         <v>46116.31139953704</v>
       </c>
       <c r="D21" s="1">
-        <v>46116.56134259259</v>
+        <v>46116.31134259259</v>
       </c>
       <c r="E21">
         <v>11422</v>
@@ -6682,7 +6682,7 @@
         <v>46116.311478159725</v>
       </c>
       <c r="D22" s="1">
-        <v>46116.561423611114</v>
+        <v>46116.311423611114</v>
       </c>
       <c r="E22">
         <v>11633</v>
@@ -6825,7 +6825,7 @@
         <v>46116.311717662036</v>
       </c>
       <c r="D23" s="1">
-        <v>46116.561689814815</v>
+        <v>46116.311689814815</v>
       </c>
       <c r="E23">
         <v>12047</v>
@@ -6968,7 +6968,7 @@
         <v>46116.31178914352</v>
       </c>
       <c r="D24" s="1">
-        <v>46116.56177083333</v>
+        <v>46116.31177083333</v>
       </c>
       <c r="E24">
         <v>12260</v>
@@ -7111,7 +7111,7 @@
         <v>46116.31209381945</v>
       </c>
       <c r="D25" s="1">
-        <v>46116.56203703704</v>
+        <v>46116.31203703704</v>
       </c>
       <c r="E25">
         <v>12726</v>
@@ -7254,7 +7254,7 @@
         <v>46116.31216451389</v>
       </c>
       <c r="D26" s="1">
-        <v>46116.56211805555</v>
+        <v>46116.31211805555</v>
       </c>
       <c r="E26">
         <v>12942</v>
@@ -7397,7 +7397,7 @@
         <v>46116.31241215278</v>
       </c>
       <c r="D27" s="1">
-        <v>46116.56238425926</v>
+        <v>46116.31238425926</v>
       </c>
       <c r="E27">
         <v>13424</v>
@@ -7540,7 +7540,7 @@
         <v>46116.31249181713</v>
       </c>
       <c r="D28" s="1">
-        <v>46116.56246527778</v>
+        <v>46116.31246527778</v>
       </c>
       <c r="E28">
         <v>13635</v>
@@ -7683,7 +7683,7 @@
         <v>46116.31278822917</v>
       </c>
       <c r="D29" s="1">
-        <v>46116.562731481485</v>
+        <v>46116.312731481485</v>
       </c>
       <c r="E29">
         <v>14094</v>
@@ -7826,7 +7826,7 @@
         <v>46116.31285991898</v>
       </c>
       <c r="D30" s="1">
-        <v>46116.5628125</v>
+        <v>46116.3128125</v>
       </c>
       <c r="E30">
         <v>14304</v>
@@ -7969,7 +7969,7 @@
         <v>46116.31310673611</v>
       </c>
       <c r="D31" s="1">
-        <v>46116.5630787037</v>
+        <v>46116.3130787037</v>
       </c>
       <c r="E31">
         <v>14758</v>
@@ -8112,7 +8112,7 @@
         <v>46116.3131778125</v>
       </c>
       <c r="D32" s="1">
-        <v>46116.563159722224</v>
+        <v>46116.313159722224</v>
       </c>
       <c r="E32">
         <v>14975</v>
@@ -8255,7 +8255,7 @@
         <v>46116.31348292824</v>
       </c>
       <c r="D33" s="1">
-        <v>46116.563425925924</v>
+        <v>46116.313425925924</v>
       </c>
       <c r="E33">
         <v>15424</v>
@@ -8398,7 +8398,7 @@
         <v>46116.313559421294</v>
       </c>
       <c r="D34" s="1">
-        <v>46116.56350694445</v>
+        <v>46116.31350694445</v>
       </c>
       <c r="E34">
         <v>15622</v>
@@ -8541,7 +8541,7 @@
         <v>46116.31380267361</v>
       </c>
       <c r="D35" s="1">
-        <v>46116.56377314815</v>
+        <v>46116.31377314815</v>
       </c>
       <c r="E35">
         <v>16094</v>
@@ -8684,7 +8684,7 @@
         <v>46116.31387248843</v>
       </c>
       <c r="D36" s="1">
-        <v>46116.56385416666</v>
+        <v>46116.31385416666</v>
       </c>
       <c r="E36">
         <v>16296</v>
@@ -8827,7 +8827,7 @@
         <v>46116.314177106484</v>
       </c>
       <c r="D37" s="1">
-        <v>46116.56412037037</v>
+        <v>46116.31412037037</v>
       </c>
       <c r="E37">
         <v>16765</v>
@@ -8970,7 +8970,7 @@
         <v>46116.314248344905</v>
       </c>
       <c r="D38" s="1">
-        <v>46116.56420138889</v>
+        <v>46116.31420138889</v>
       </c>
       <c r="E38">
         <v>16988</v>
@@ -9113,7 +9113,7 @@
         <v>46116.314495659724</v>
       </c>
       <c r="D39" s="1">
-        <v>46116.564467592594</v>
+        <v>46116.314467592594</v>
       </c>
       <c r="E39">
         <v>17476</v>
@@ -9256,7 +9256,7 @@
         <v>46116.31456684028</v>
       </c>
       <c r="D40" s="1">
-        <v>46116.56454861111</v>
+        <v>46116.31454861111</v>
       </c>
       <c r="E40">
         <v>17668</v>
@@ -9399,7 +9399,7 @@
         <v>46116.31487199074</v>
       </c>
       <c r="D41" s="1">
-        <v>46116.56481481482</v>
+        <v>46116.31481481482</v>
       </c>
       <c r="E41">
         <v>18113</v>
@@ -9542,7 +9542,7 @@
         <v>46116.31494975695</v>
       </c>
       <c r="D42" s="1">
-        <v>46116.56489583333</v>
+        <v>46116.31489583333</v>
       </c>
       <c r="E42">
         <v>18333</v>
@@ -9685,7 +9685,7 @@
         <v>46116.31518994213</v>
       </c>
       <c r="D43" s="1">
-        <v>46116.56516203703</v>
+        <v>46116.31516203703</v>
       </c>
       <c r="E43">
         <v>18813</v>
@@ -9828,7 +9828,7 @@
         <v>46116.315261979165</v>
       </c>
       <c r="D44" s="1">
-        <v>46116.56524305556</v>
+        <v>46116.31524305556</v>
       </c>
       <c r="E44">
         <v>19026</v>
@@ -9971,7 +9971,7 @@
         <v>46116.315566157406</v>
       </c>
       <c r="D45" s="1">
-        <v>46116.56550925926</v>
+        <v>46116.31550925926</v>
       </c>
       <c r="E45">
         <v>19520</v>
@@ -10114,7 +10114,7 @@
         <v>46116.31563775463</v>
       </c>
       <c r="D46" s="1">
-        <v>46116.56559027778</v>
+        <v>46116.31559027778</v>
       </c>
       <c r="E46">
         <v>19747</v>
@@ -10257,7 +10257,7 @@
         <v>46116.31588457176</v>
       </c>
       <c r="D47" s="1">
-        <v>46116.56585648148</v>
+        <v>46116.31585648148</v>
       </c>
       <c r="E47">
         <v>20249</v>
@@ -10400,7 +10400,7 @@
         <v>46116.31595630787</v>
       </c>
       <c r="D48" s="1">
-        <v>46116.5659375</v>
+        <v>46116.3159375</v>
       </c>
       <c r="E48">
         <v>20473</v>
@@ -10543,7 +10543,7 @@
         <v>46116.316261087966</v>
       </c>
       <c r="D49" s="1">
-        <v>46116.566203703704</v>
+        <v>46116.316203703704</v>
       </c>
       <c r="E49">
         <v>20945</v>
@@ -10686,7 +10686,7 @@
         <v>46116.31633226852</v>
       </c>
       <c r="D50" s="1">
-        <v>46116.56628472222</v>
+        <v>46116.31628472222</v>
       </c>
       <c r="E50">
         <v>21173</v>
@@ -10829,7 +10829,7 @@
         <v>46116.31657916667</v>
       </c>
       <c r="D51" s="1">
-        <v>46116.56655092593</v>
+        <v>46116.31655092593</v>
       </c>
       <c r="E51">
         <v>21684</v>
@@ -10972,7 +10972,7 @@
         <v>46116.316658993055</v>
       </c>
       <c r="D52" s="1">
-        <v>46116.56663194444</v>
+        <v>46116.31663194444</v>
       </c>
       <c r="E52">
         <v>21913</v>
@@ -11115,7 +11115,7 @@
         <v>46116.31695633102</v>
       </c>
       <c r="D53" s="1">
-        <v>46116.56689814815</v>
+        <v>46116.31689814815</v>
       </c>
       <c r="E53">
         <v>22424</v>
@@ -11258,7 +11258,7 @@
         <v>46116.31727380787</v>
       </c>
       <c r="D54" s="1">
-        <v>46116.567245370374</v>
+        <v>46116.317245370374</v>
       </c>
       <c r="E54">
         <v>23169</v>
@@ -11401,7 +11401,7 @@
         <v>46116.31734504629</v>
       </c>
       <c r="D55" s="1">
-        <v>46116.56732638889</v>
+        <v>46116.31732638889</v>
       </c>
       <c r="E55">
         <v>23402</v>
@@ -11544,7 +11544,7 @@
         <v>46116.317649641205</v>
       </c>
       <c r="D56" s="1">
-        <v>46116.56759259259</v>
+        <v>46116.31759259259</v>
       </c>
       <c r="E56">
         <v>23926</v>
@@ -11687,7 +11687,7 @@
         <v>46116.31773019676</v>
       </c>
       <c r="D57" s="1">
-        <v>46116.56767361111</v>
+        <v>46116.31767361111</v>
       </c>
       <c r="E57">
         <v>24147</v>
@@ -11830,7 +11830,7 @@
         <v>46116.31796872685</v>
       </c>
       <c r="D58" s="1">
-        <v>46116.56793981481</v>
+        <v>46116.31793981481</v>
       </c>
       <c r="E58">
         <v>24711</v>
@@ -11973,7 +11973,7 @@
         <v>46116.31803944444</v>
       </c>
       <c r="D59" s="1">
-        <v>46116.568020833336</v>
+        <v>46116.318020833336</v>
       </c>
       <c r="E59">
         <v>24906</v>
@@ -12116,7 +12116,7 @@
         <v>46116.318345416665</v>
       </c>
       <c r="D60" s="1">
-        <v>46116.56828703704</v>
+        <v>46116.31828703704</v>
       </c>
       <c r="E60">
         <v>25464</v>
@@ -12259,7 +12259,7 @@
         <v>46116.318415925925</v>
       </c>
       <c r="D61" s="1">
-        <v>46116.56836805555</v>
+        <v>46116.31836805555</v>
       </c>
       <c r="E61">
         <v>25696</v>
@@ -12402,7 +12402,7 @@
         <v>46116.3186625</v>
       </c>
       <c r="D62" s="1">
-        <v>46116.56863425926</v>
+        <v>46116.31863425926</v>
       </c>
       <c r="E62">
         <v>26219</v>
@@ -12545,7 +12545,7 @@
         <v>46116.318734594905</v>
       </c>
       <c r="D63" s="1">
-        <v>46116.568715277775</v>
+        <v>46116.318715277775</v>
       </c>
       <c r="E63">
         <v>26463</v>
@@ -12688,7 +12688,7 @@
         <v>46116.319041469906</v>
       </c>
       <c r="D64" s="1">
-        <v>46116.56898148148</v>
+        <v>46116.31898148148</v>
       </c>
       <c r="E64">
         <v>27001</v>
@@ -12831,7 +12831,7 @@
         <v>46116.31911675926</v>
       </c>
       <c r="D65" s="1">
-        <v>46116.5690625</v>
+        <v>46116.3190625</v>
       </c>
       <c r="E65">
         <v>27234</v>
@@ -12974,7 +12974,7 @@
         <v>46116.31935709491</v>
       </c>
       <c r="D66" s="1">
-        <v>46116.56932870371</v>
+        <v>46116.31932870371</v>
       </c>
       <c r="E66">
         <v>27840</v>
@@ -13117,7 +13117,7 @@
         <v>46116.31943732639</v>
       </c>
       <c r="D67" s="1">
-        <v>46116.56940972222</v>
+        <v>46116.31940972222</v>
       </c>
       <c r="E67">
         <v>28095</v>
@@ -13260,7 +13260,7 @@
         <v>46116.31973318287</v>
       </c>
       <c r="D68" s="1">
-        <v>46116.56967592592</v>
+        <v>46116.31967592592</v>
       </c>
       <c r="E68">
         <v>28705</v>
@@ -13403,7 +13403,7 @@
         <v>46116.319816076386</v>
       </c>
       <c r="D69" s="1">
-        <v>46116.569756944446</v>
+        <v>46116.319756944446</v>
       </c>
       <c r="E69">
         <v>28941</v>
@@ -13546,7 +13546,7 @@
         <v>46116.32005133102</v>
       </c>
       <c r="D70" s="1">
-        <v>46116.570023148146</v>
+        <v>46116.320023148146</v>
       </c>
       <c r="E70">
         <v>29517</v>
@@ -13689,7 +13689,7 @@
         <v>46116.32012351852</v>
       </c>
       <c r="D71" s="1">
-        <v>46116.57010416667</v>
+        <v>46116.32010416667</v>
       </c>
       <c r="E71">
         <v>29719</v>
@@ -13832,7 +13832,7 @@
         <v>46116.32042787037</v>
       </c>
       <c r="D72" s="1">
-        <v>46116.57037037037</v>
+        <v>46116.32037037037</v>
       </c>
       <c r="E72">
         <v>30208</v>
@@ -13975,7 +13975,7 @@
         <v>46116.32050398148</v>
       </c>
       <c r="D73" s="1">
-        <v>46116.57045138889</v>
+        <v>46116.32045138889</v>
       </c>
       <c r="E73">
         <v>30453</v>
@@ -14118,7 +14118,7 @@
         <v>46116.32074611111</v>
       </c>
       <c r="D74" s="1">
-        <v>46116.57071759259</v>
+        <v>46116.32071759259</v>
       </c>
       <c r="E74">
         <v>30873</v>
@@ -14261,7 +14261,7 @@
         <v>46116.32081680556</v>
       </c>
       <c r="D75" s="1">
-        <v>46116.57079861111</v>
+        <v>46116.32079861111</v>
       </c>
       <c r="E75">
         <v>31104</v>
@@ -14404,7 +14404,7 @@
         <v>46116.32112199074</v>
       </c>
       <c r="D76" s="1">
-        <v>46116.571064814816</v>
+        <v>46116.321064814816</v>
       </c>
       <c r="E76">
         <v>31619</v>
@@ -14547,7 +14547,7 @@
         <v>46116.32120533565</v>
       </c>
       <c r="D77" s="1">
-        <v>46116.57114583333</v>
+        <v>46116.32114583333</v>
       </c>
       <c r="E77">
         <v>31817</v>
@@ -14690,7 +14690,7 @@
         <v>46116.32144056713</v>
       </c>
       <c r="D78" s="1">
-        <v>46116.57141203704</v>
+        <v>46116.32141203704</v>
       </c>
       <c r="E78">
         <v>32254</v>
@@ -14833,7 +14833,7 @@
         <v>46116.32151175926</v>
       </c>
       <c r="D79" s="1">
-        <v>46116.571493055555</v>
+        <v>46116.321493055555</v>
       </c>
       <c r="E79">
         <v>32474</v>
@@ -14976,7 +14976,7 @@
         <v>46116.32181681713</v>
       </c>
       <c r="D80" s="1">
-        <v>46116.57175925926</v>
+        <v>46116.32175925926</v>
       </c>
       <c r="E80">
         <v>32966</v>
@@ -15119,7 +15119,7 @@
         <v>46116.32188855324</v>
       </c>
       <c r="D81" s="1">
-        <v>46116.57184027778</v>
+        <v>46116.32184027778</v>
       </c>
       <c r="E81">
         <v>33193</v>
@@ -15262,7 +15262,7 @@
         <v>46116.32213502315</v>
       </c>
       <c r="D82" s="1">
-        <v>46116.57210648148</v>
+        <v>46116.32210648148</v>
       </c>
       <c r="E82">
         <v>33759</v>
@@ -15405,7 +15405,7 @@
         <v>46116.32221675926</v>
       </c>
       <c r="D83" s="1">
-        <v>46116.5721875</v>
+        <v>46116.3221875</v>
       </c>
       <c r="E83">
         <v>33995</v>
@@ -15548,7 +15548,7 @@
         <v>46116.32251131944</v>
       </c>
       <c r="D84" s="1">
-        <v>46116.5724537037</v>
+        <v>46116.3224537037</v>
       </c>
       <c r="E84">
         <v>34514</v>
@@ -15691,7 +15691,7 @@
         <v>46116.322586608796</v>
       </c>
       <c r="D85" s="1">
-        <v>46116.572534722225</v>
+        <v>46116.322534722225</v>
       </c>
       <c r="E85">
         <v>34749</v>
@@ -15834,7 +15834,7 @@
         <v>46116.322829351855</v>
       </c>
       <c r="D86" s="1">
-        <v>46116.572800925926</v>
+        <v>46116.322800925926</v>
       </c>
       <c r="E86">
         <v>35323</v>
@@ -15977,7 +15977,7 @@
         <v>46116.322900046296</v>
       </c>
       <c r="D87" s="1">
-        <v>46116.57288194444</v>
+        <v>46116.32288194444</v>
       </c>
       <c r="E87">
         <v>35586</v>
@@ -16120,7 +16120,7 @@
         <v>46116.32320554398</v>
       </c>
       <c r="D88" s="1">
-        <v>46116.57314814815</v>
+        <v>46116.32314814815</v>
       </c>
       <c r="E88">
         <v>36304</v>
@@ -16263,7 +16263,7 @@
         <v>46116.323287673615</v>
       </c>
       <c r="D89" s="1">
-        <v>46116.573229166665</v>
+        <v>46116.323229166665</v>
       </c>
       <c r="E89">
         <v>36549</v>
@@ -16406,7 +16406,7 @@
         <v>46116.32352391204</v>
       </c>
       <c r="D90" s="1">
-        <v>46116.57349537037</v>
+        <v>46116.32349537037</v>
       </c>
       <c r="E90">
         <v>37164</v>
@@ -16549,7 +16549,7 @@
         <v>46116.323598229166</v>
       </c>
       <c r="D91" s="1">
-        <v>46116.57357638889</v>
+        <v>46116.32357638889</v>
       </c>
       <c r="E91">
         <v>37442</v>
@@ -16692,7 +16692,7 @@
         <v>46116.323899965275</v>
       </c>
       <c r="D92" s="1">
-        <v>46116.573842592596</v>
+        <v>46116.323842592596</v>
       </c>
       <c r="E92">
         <v>38164</v>
@@ -16835,7 +16835,7 @@
         <v>46116.32397024306</v>
       </c>
       <c r="D93" s="1">
-        <v>46116.57392361111</v>
+        <v>46116.32392361111</v>
       </c>
       <c r="E93">
         <v>38384</v>
@@ -16978,7 +16978,7 @@
         <v>46116.3242183912</v>
       </c>
       <c r="D94" s="1">
-        <v>46116.57418981481</v>
+        <v>46116.32418981481</v>
       </c>
       <c r="E94">
         <v>39041</v>
@@ -17121,7 +17121,7 @@
         <v>46116.32429011574</v>
       </c>
       <c r="D95" s="1">
-        <v>46116.574270833335</v>
+        <v>46116.324270833335</v>
       </c>
       <c r="E95">
         <v>39314</v>
@@ -17264,7 +17264,7 @@
         <v>46116.32459471065</v>
       </c>
       <c r="D96" s="1">
-        <v>46116.574537037035</v>
+        <v>46116.324537037035</v>
       </c>
       <c r="E96">
         <v>39935</v>
@@ -17407,7 +17407,7 @@
         <v>46116.324662824074</v>
       </c>
       <c r="D97" s="1">
-        <v>46116.57461805556</v>
+        <v>46116.32461805556</v>
       </c>
       <c r="E97">
         <v>40182</v>
@@ -17550,7 +17550,7 @@
         <v>46116.32491319445</v>
       </c>
       <c r="D98" s="1">
-        <v>46116.57488425926</v>
+        <v>46116.32488425926</v>
       </c>
       <c r="E98">
         <v>40713</v>
@@ -17693,7 +17693,7 @@
         <v>46116.32498306713</v>
       </c>
       <c r="D99" s="1">
-        <v>46116.57496527778</v>
+        <v>46116.32496527778</v>
       </c>
       <c r="E99">
         <v>40955</v>
@@ -17836,7 +17836,7 @@
         <v>46116.32528916666</v>
       </c>
       <c r="D100" s="1">
-        <v>46116.57523148148</v>
+        <v>46116.32523148148</v>
       </c>
       <c r="E100">
         <v>41543</v>
@@ -17979,7 +17979,7 @@
         <v>46116.32536783565</v>
       </c>
       <c r="D101" s="1">
-        <v>46116.5753125</v>
+        <v>46116.3253125</v>
       </c>
       <c r="E101">
         <v>41757</v>
@@ -18122,7 +18122,7 @@
         <v>46116.325607280094</v>
       </c>
       <c r="D102" s="1">
-        <v>46116.575578703705</v>
+        <v>46116.325578703705</v>
       </c>
       <c r="E102">
         <v>42224</v>
@@ -18265,7 +18265,7 @@
         <v>46116.32568913195</v>
       </c>
       <c r="D103" s="1">
-        <v>46116.57565972222</v>
+        <v>46116.32565972222</v>
       </c>
       <c r="E103">
         <v>42465</v>
@@ -18408,7 +18408,7 @@
         <v>46116.32598363426</v>
       </c>
       <c r="D104" s="1">
-        <v>46116.57592592593</v>
+        <v>46116.32592592593</v>
       </c>
       <c r="E104">
         <v>42788</v>
@@ -18551,7 +18551,7 @@
         <v>46116.32605328703</v>
       </c>
       <c r="D105" s="1">
-        <v>46116.576006944444</v>
+        <v>46116.326006944444</v>
       </c>
       <c r="E105">
         <v>42960</v>
@@ -18694,7 +18694,7 @@
         <v>46116.326302106485</v>
       </c>
       <c r="D106" s="1">
-        <v>46116.576273148145</v>
+        <v>46116.326273148145</v>
       </c>
       <c r="E106">
         <v>43475</v>
@@ -18837,7 +18837,7 @@
         <v>46116.3263733912</v>
       </c>
       <c r="D107" s="1">
-        <v>46116.57635416667</v>
+        <v>46116.32635416667</v>
       </c>
       <c r="E107">
         <v>43748</v>
@@ -18980,7 +18980,7 @@
         <v>46116.32667229167</v>
       </c>
       <c r="D108" s="1">
-        <v>46116.57662037037</v>
+        <v>46116.32662037037</v>
       </c>
       <c r="E108">
         <v>44405</v>
@@ -19123,7 +19123,7 @@
         <v>46116.32675224537</v>
       </c>
       <c r="D109" s="1">
-        <v>46116.57670138889</v>
+        <v>46116.32670138889</v>
       </c>
       <c r="E109">
         <v>44628</v>
@@ -19266,7 +19266,7 @@
         <v>46116.32699275463</v>
       </c>
       <c r="D110" s="1">
-        <v>46116.57696759259</v>
+        <v>46116.32696759259</v>
       </c>
       <c r="E110">
         <v>44986</v>
@@ -19409,7 +19409,7 @@
         <v>46116.327065046295</v>
       </c>
       <c r="D111" s="1">
-        <v>46116.577048611114</v>
+        <v>46116.327048611114</v>
       </c>
       <c r="E111">
         <v>45226</v>
@@ -19552,7 +19552,7 @@
         <v>46116.327368819446</v>
       </c>
       <c r="D112" s="1">
-        <v>46116.577314814815</v>
+        <v>46116.327314814815</v>
       </c>
       <c r="E112">
         <v>45577</v>
@@ -19695,7 +19695,7 @@
         <v>46116.327451377314</v>
       </c>
       <c r="D113" s="1">
-        <v>46116.57739583333</v>
+        <v>46116.32739583333</v>
       </c>
       <c r="E113">
         <v>45841</v>
@@ -19838,7 +19838,7 @@
         <v>46116.32768738426</v>
       </c>
       <c r="D114" s="1">
-        <v>46116.57766203704</v>
+        <v>46116.32766203704</v>
       </c>
       <c r="E114">
         <v>46216</v>
@@ -19981,7 +19981,7 @@
         <v>46116.32776269676</v>
       </c>
       <c r="D115" s="1">
-        <v>46116.57774305555</v>
+        <v>46116.32774305555</v>
       </c>
       <c r="E115">
         <v>46448</v>
@@ -20124,7 +20124,7 @@
         <v>46116.32806325232</v>
       </c>
       <c r="D116" s="1">
-        <v>46116.57800925926</v>
+        <v>46116.32800925926</v>
       </c>
       <c r="E116">
         <v>46979</v>
@@ -20267,7 +20267,7 @@
         <v>46116.32813627315</v>
       </c>
       <c r="D117" s="1">
-        <v>46116.57809027778</v>
+        <v>46116.32809027778</v>
       </c>
       <c r="E117">
         <v>47182</v>
@@ -20410,7 +20410,7 @@
         <v>46116.32838179398</v>
       </c>
       <c r="D118" s="1">
-        <v>46116.578356481485</v>
+        <v>46116.328356481485</v>
       </c>
       <c r="E118">
         <v>47646</v>
@@ -20553,7 +20553,7 @@
         <v>46116.32846340278</v>
       </c>
       <c r="D119" s="1">
-        <v>46116.5784375</v>
+        <v>46116.3284375</v>
       </c>
       <c r="E119">
         <v>47831</v>
@@ -20696,7 +20696,7 @@
         <v>46116.3287578125</v>
       </c>
       <c r="D120" s="1">
-        <v>46116.5787037037</v>
+        <v>46116.3287037037</v>
       </c>
       <c r="E120">
         <v>48231</v>
@@ -20839,7 +20839,7 @@
         <v>46116.328834155094</v>
       </c>
       <c r="D121" s="1">
-        <v>46116.578784722224</v>
+        <v>46116.328784722224</v>
       </c>
       <c r="E121">
         <v>48473</v>
@@ -20982,7 +20982,7 @@
         <v>46116.329076319445</v>
       </c>
       <c r="D122" s="1">
-        <v>46116.579050925924</v>
+        <v>46116.329050925924</v>
       </c>
       <c r="E122">
         <v>49064</v>
@@ -21125,7 +21125,7 @@
         <v>46116.32915247685</v>
       </c>
       <c r="D123" s="1">
-        <v>46116.57913194445</v>
+        <v>46116.32913194445</v>
       </c>
       <c r="E123">
         <v>49356</v>
@@ -21268,7 +21268,7 @@
         <v>46116.32945253472</v>
       </c>
       <c r="D124" s="1">
-        <v>46116.57939814815</v>
+        <v>46116.32939814815</v>
       </c>
       <c r="E124">
         <v>49918</v>
@@ -21411,7 +21411,7 @@
         <v>46116.32952861111</v>
       </c>
       <c r="D125" s="1">
-        <v>46116.57947916666</v>
+        <v>46116.32947916666</v>
       </c>
       <c r="E125">
         <v>50161</v>
@@ -21554,7 +21554,7 @@
         <v>46116.329770902776</v>
       </c>
       <c r="D126" s="1">
-        <v>46116.57974537037</v>
+        <v>46116.32974537037</v>
       </c>
       <c r="E126">
         <v>50749</v>
@@ -21697,7 +21697,7 @@
         <v>46116.32984519676</v>
       </c>
       <c r="D127" s="1">
-        <v>46116.57982638889</v>
+        <v>46116.32982638889</v>
       </c>
       <c r="E127">
         <v>51001</v>
@@ -21840,7 +21840,7 @@
         <v>46116.330146643515</v>
       </c>
       <c r="D128" s="1">
-        <v>46116.580092592594</v>
+        <v>46116.330092592594</v>
       </c>
       <c r="E128">
         <v>51529</v>
@@ -21983,7 +21983,7 @@
         <v>46116.330226666665</v>
       </c>
       <c r="D129" s="1">
-        <v>46116.58017361111</v>
+        <v>46116.33017361111</v>
       </c>
       <c r="E129">
         <v>51761</v>
@@ -22126,7 +22126,7 @@
         <v>46116.33046520833</v>
       </c>
       <c r="D130" s="1">
-        <v>46116.58043981482</v>
+        <v>46116.33043981482</v>
       </c>
       <c r="E130">
         <v>52299</v>
@@ -22269,7 +22269,7 @@
         <v>46116.33054216435</v>
       </c>
       <c r="D131" s="1">
-        <v>46116.58052083333</v>
+        <v>46116.33052083333</v>
       </c>
       <c r="E131">
         <v>52479</v>
@@ -22412,7 +22412,7 @@
         <v>46116.33084229167</v>
       </c>
       <c r="D132" s="1">
-        <v>46116.58078703703</v>
+        <v>46116.33078703703</v>
       </c>
       <c r="E132">
         <v>52975</v>
@@ -22555,7 +22555,7 @@
         <v>46116.33091834491</v>
       </c>
       <c r="D133" s="1">
-        <v>46116.58086805556</v>
+        <v>46116.33086805556</v>
       </c>
       <c r="E133">
         <v>53236</v>
@@ -22698,7 +22698,7 @@
         <v>46116.33116040509</v>
       </c>
       <c r="D134" s="1">
-        <v>46116.58113425926</v>
+        <v>46116.33113425926</v>
       </c>
       <c r="E134">
         <v>53796</v>
@@ -22841,7 +22841,7 @@
         <v>46116.331536412035</v>
       </c>
       <c r="D135" s="1">
-        <v>46116.58148148148</v>
+        <v>46116.33148148148</v>
       </c>
       <c r="E135">
         <v>54501</v>
@@ -22984,7 +22984,7 @@
         <v>46116.3316109375</v>
       </c>
       <c r="D136" s="1">
-        <v>46116.5815625</v>
+        <v>46116.3315625</v>
       </c>
       <c r="E136">
         <v>54681</v>
@@ -23127,7 +23127,7 @@
         <v>46116.33185517361</v>
       </c>
       <c r="D137" s="1">
-        <v>46116.581828703704</v>
+        <v>46116.331828703704</v>
       </c>
       <c r="E137">
         <v>55046</v>
@@ -23270,7 +23270,7 @@
         <v>46116.33192701389</v>
       </c>
       <c r="D138" s="1">
-        <v>46116.58190972222</v>
+        <v>46116.33190972222</v>
       </c>
       <c r="E138">
         <v>55236</v>
@@ -23413,7 +23413,7 @@
         <v>46116.33230607639</v>
       </c>
       <c r="D139" s="1">
-        <v>46116.58225694444</v>
+        <v>46116.33225694444</v>
       </c>
       <c r="E139">
         <v>55796</v>
@@ -23556,7 +23556,7 @@
         <v>46116.33254950232</v>
       </c>
       <c r="D140" s="1">
-        <v>46116.58252314815</v>
+        <v>46116.33252314815</v>
       </c>
       <c r="E140">
         <v>56189</v>
@@ -23699,7 +23699,7 @@
         <v>46116.332624965275</v>
       </c>
       <c r="D141" s="1">
-        <v>46116.582604166666</v>
+        <v>46116.332604166666</v>
       </c>
       <c r="E141">
         <v>56372</v>
@@ -23842,7 +23842,7 @@
         <v>46116.33292543981</v>
       </c>
       <c r="D142" s="1">
-        <v>46116.582870370374</v>
+        <v>46116.332870370374</v>
       </c>
       <c r="E142">
         <v>56703</v>
@@ -23985,7 +23985,7 @@
         <v>46116.33299776621</v>
       </c>
       <c r="D143" s="1">
-        <v>46116.58295138889</v>
+        <v>46116.33295138889</v>
       </c>
       <c r="E143">
         <v>56858</v>
@@ -24128,7 +24128,7 @@
         <v>46116.33324396991</v>
       </c>
       <c r="D144" s="1">
-        <v>46116.58321759259</v>
+        <v>46116.33321759259</v>
       </c>
       <c r="E144">
         <v>57248</v>
@@ -24271,7 +24271,7 @@
         <v>46116.33331674769</v>
       </c>
       <c r="D145" s="1">
-        <v>46116.58329861111</v>
+        <v>46116.33329861111</v>
       </c>
       <c r="E145">
         <v>57452</v>
@@ -24414,7 +24414,7 @@
         <v>46116.33361984954</v>
       </c>
       <c r="D146" s="1">
-        <v>46116.58356481481</v>
+        <v>46116.33356481481</v>
       </c>
       <c r="E146">
         <v>57932</v>
@@ -24557,7 +24557,7 @@
         <v>46116.33369533565</v>
       </c>
       <c r="D147" s="1">
-        <v>46116.583645833336</v>
+        <v>46116.333645833336</v>
       </c>
       <c r="E147">
         <v>58136</v>
@@ -24700,7 +24700,7 @@
         <v>46116.33393855324</v>
       </c>
       <c r="D148" s="1">
-        <v>46116.58391203704</v>
+        <v>46116.33391203704</v>
       </c>
       <c r="E148">
         <v>58694</v>
@@ -24843,7 +24843,7 @@
         <v>46116.33401212963</v>
       </c>
       <c r="D149" s="1">
-        <v>46116.58399305555</v>
+        <v>46116.33399305555</v>
       </c>
       <c r="E149">
         <v>58967</v>
@@ -24986,7 +24986,7 @@
         <v>46116.33431425926</v>
       </c>
       <c r="D150" s="1">
-        <v>46116.58425925926</v>
+        <v>46116.33425925926</v>
       </c>
       <c r="E150">
         <v>59434</v>
@@ -25129,7 +25129,7 @@
         <v>46116.33463300926</v>
       </c>
       <c r="D151" s="1">
-        <v>46116.58460648148</v>
+        <v>46116.33460648148</v>
       </c>
       <c r="E151">
         <v>60037</v>
@@ -25272,7 +25272,7 @@
         <v>46116.33471018518</v>
       </c>
       <c r="D152" s="1">
-        <v>46116.5846875</v>
+        <v>46116.3346875</v>
       </c>
       <c r="E152">
         <v>60217</v>
@@ -25415,7 +25415,7 @@
         <v>46116.335008738424</v>
       </c>
       <c r="D153" s="1">
-        <v>46116.58495370371</v>
+        <v>46116.33495370371</v>
       </c>
       <c r="E153">
         <v>60497</v>
@@ -25558,7 +25558,7 @@
         <v>46116.335085625</v>
       </c>
       <c r="D154" s="1">
-        <v>46116.58503472222</v>
+        <v>46116.33503472222</v>
       </c>
       <c r="E154">
         <v>60721</v>
@@ -25701,7 +25701,7 @@
         <v>46116.33532825232</v>
       </c>
       <c r="D155" s="1">
-        <v>46116.58530092592</v>
+        <v>46116.33530092592</v>
       </c>
       <c r="E155">
         <v>61321</v>
@@ -25844,7 +25844,7 @@
         <v>46116.33539893518</v>
       </c>
       <c r="D156" s="1">
-        <v>46116.585381944446</v>
+        <v>46116.335381944446</v>
       </c>
       <c r="E156">
         <v>61492</v>
@@ -25987,7 +25987,7 @@
         <v>46116.335703125</v>
       </c>
       <c r="D157" s="1">
-        <v>46116.585648148146</v>
+        <v>46116.335648148146</v>
       </c>
       <c r="E157">
         <v>61940</v>
@@ -26130,7 +26130,7 @@
         <v>46116.33577210648</v>
       </c>
       <c r="D158" s="1">
-        <v>46116.58572916667</v>
+        <v>46116.33572916667</v>
       </c>
       <c r="E158">
         <v>62177</v>
@@ -26273,7 +26273,7 @@
         <v>46116.33602166667</v>
       </c>
       <c r="D159" s="1">
-        <v>46116.58599537037</v>
+        <v>46116.33599537037</v>
       </c>
       <c r="E159">
         <v>62834</v>
@@ -26416,7 +26416,7 @@
         <v>46116.336099305554</v>
       </c>
       <c r="D160" s="1">
-        <v>46116.58607638889</v>
+        <v>46116.33607638889</v>
       </c>
       <c r="E160">
         <v>62992</v>
@@ -26562,7 +26562,7 @@
         <v>46116.3363980787</v>
       </c>
       <c r="D161" s="1">
-        <v>46116.58634259259</v>
+        <v>46116.33634259259</v>
       </c>
       <c r="E161">
         <v>63355</v>
@@ -26705,7 +26705,7 @@
         <v>46116.336472083334</v>
       </c>
       <c r="D162" s="1">
-        <v>46116.58642361111</v>
+        <v>46116.33642361111</v>
       </c>
       <c r="E162">
         <v>63545</v>
@@ -26848,7 +26848,7 @@
         <v>46116.33671592593</v>
       </c>
       <c r="D163" s="1">
-        <v>46116.586689814816</v>
+        <v>46116.336689814816</v>
       </c>
       <c r="E163">
         <v>63881</v>
@@ -26991,7 +26991,7 @@
         <v>46116.33678856481</v>
       </c>
       <c r="D164" s="1">
-        <v>46116.58677083333</v>
+        <v>46116.33677083333</v>
       </c>
       <c r="E164">
         <v>64089</v>
@@ -27134,7 +27134,7 @@
         <v>46116.337092395835</v>
       </c>
       <c r="D165" s="1">
-        <v>46116.58703703704</v>
+        <v>46116.33703703704</v>
       </c>
       <c r="E165">
         <v>64444</v>
@@ -27277,7 +27277,7 @@
         <v>46116.33716178241</v>
       </c>
       <c r="D166" s="1">
-        <v>46116.587118055555</v>
+        <v>46116.337118055555</v>
       </c>
       <c r="E166">
         <v>64606</v>
@@ -27420,7 +27420,7 @@
         <v>46116.33741075231</v>
       </c>
       <c r="D167" s="1">
-        <v>46116.58738425926</v>
+        <v>46116.33738425926</v>
       </c>
       <c r="E167">
         <v>64878</v>
@@ -27563,7 +27563,7 @@
         <v>46116.3374859375</v>
       </c>
       <c r="D168" s="1">
-        <v>46116.58746527778</v>
+        <v>46116.33746527778</v>
       </c>
       <c r="E168">
         <v>65054</v>
@@ -27706,7 +27706,7 @@
         <v>46116.33778685185</v>
       </c>
       <c r="D169" s="1">
-        <v>46116.58773148148</v>
+        <v>46116.33773148148</v>
       </c>
       <c r="E169">
         <v>65350</v>
@@ -27849,7 +27849,7 @@
         <v>46116.3378534838</v>
       </c>
       <c r="D170" s="1">
-        <v>46116.5878125</v>
+        <v>46116.3378125</v>
       </c>
       <c r="E170">
         <v>65522</v>
@@ -27992,7 +27992,7 @@
         <v>46116.33810511574</v>
       </c>
       <c r="D171" s="1">
-        <v>46116.5880787037</v>
+        <v>46116.3380787037</v>
       </c>
       <c r="E171">
         <v>65797</v>
@@ -28135,7 +28135,7 @@
         <v>46116.338181342595</v>
       </c>
       <c r="D172" s="1">
-        <v>46116.588159722225</v>
+        <v>46116.338159722225</v>
       </c>
       <c r="E172">
         <v>65957</v>
@@ -28278,7 +28278,7 @@
         <v>46116.33848128472</v>
       </c>
       <c r="D173" s="1">
-        <v>46116.588425925926</v>
+        <v>46116.338425925926</v>
       </c>
       <c r="E173">
         <v>66330</v>
@@ -28421,7 +28421,7 @@
         <v>46116.33855143518</v>
       </c>
       <c r="D174" s="1">
-        <v>46116.58850694444</v>
+        <v>46116.33850694444</v>
       </c>
       <c r="E174">
         <v>66494</v>
@@ -28564,7 +28564,7 @@
         <v>46116.338799930556</v>
       </c>
       <c r="D175" s="1">
-        <v>46116.58877314815</v>
+        <v>46116.33877314815</v>
       </c>
       <c r="E175">
         <v>66771</v>
@@ -28707,7 +28707,7 @@
         <v>46116.338873009256</v>
       </c>
       <c r="D176" s="1">
-        <v>46116.588854166665</v>
+        <v>46116.338854166665</v>
       </c>
       <c r="E176">
         <v>66945</v>
@@ -28850,7 +28850,7 @@
         <v>46116.33917582176</v>
       </c>
       <c r="D177" s="1">
-        <v>46116.58912037037</v>
+        <v>46116.33912037037</v>
       </c>
       <c r="E177">
         <v>67243</v>
@@ -28993,7 +28993,7 @@
         <v>46116.33924291666</v>
       </c>
       <c r="D178" s="1">
-        <v>46116.58920138889</v>
+        <v>46116.33920138889</v>
       </c>
       <c r="E178">
         <v>67420</v>
@@ -29136,7 +29136,7 @@
         <v>46116.33949384259</v>
       </c>
       <c r="D179" s="1">
-        <v>46116.589467592596</v>
+        <v>46116.339467592596</v>
       </c>
       <c r="E179">
         <v>67765</v>
@@ -29279,7 +29279,7 @@
         <v>46116.339571689816</v>
       </c>
       <c r="D180" s="1">
-        <v>46116.58954861111</v>
+        <v>46116.33954861111</v>
       </c>
       <c r="E180">
         <v>67952</v>
@@ -29422,7 +29422,7 @@
         <v>46116.33987045139</v>
       </c>
       <c r="D181" s="1">
-        <v>46116.58981481481</v>
+        <v>46116.33981481481</v>
       </c>
       <c r="E181">
         <v>68363</v>
@@ -29565,7 +29565,7 @@
         <v>46116.33994366898</v>
       </c>
       <c r="D182" s="1">
-        <v>46116.589895833335</v>
+        <v>46116.339895833335</v>
       </c>
       <c r="E182">
         <v>68564</v>
@@ -29708,7 +29708,7 @@
         <v>46116.340188738424</v>
       </c>
       <c r="D183" s="1">
-        <v>46116.590162037035</v>
+        <v>46116.340162037035</v>
       </c>
       <c r="E183">
         <v>68939</v>
@@ -29851,7 +29851,7 @@
         <v>46116.34026017361</v>
       </c>
       <c r="D184" s="1">
-        <v>46116.59024305556</v>
+        <v>46116.34024305556</v>
       </c>
       <c r="E184">
         <v>69125</v>
@@ -29994,7 +29994,7 @@
         <v>46116.34056486111</v>
       </c>
       <c r="D185" s="1">
-        <v>46116.59050925926</v>
+        <v>46116.34050925926</v>
       </c>
       <c r="E185">
         <v>69463</v>
@@ -30137,7 +30137,7 @@
         <v>46116.34063310185</v>
       </c>
       <c r="D186" s="1">
-        <v>46116.59059027778</v>
+        <v>46116.34059027778</v>
       </c>
       <c r="E186">
         <v>69634</v>
@@ -30280,7 +30280,7 @@
         <v>46116.34088425926</v>
       </c>
       <c r="D187" s="1">
-        <v>46116.59085648148</v>
+        <v>46116.34085648148</v>
       </c>
       <c r="E187">
         <v>69971</v>
@@ -30423,7 +30423,7 @@
         <v>46116.340958506946</v>
       </c>
       <c r="D188" s="1">
-        <v>46116.5909375</v>
+        <v>46116.3409375</v>
       </c>
       <c r="E188">
         <v>70159</v>
@@ -30566,7 +30566,7 @@
         <v>46116.341259166664</v>
       </c>
       <c r="D189" s="1">
-        <v>46116.591203703705</v>
+        <v>46116.341203703705</v>
       </c>
       <c r="E189">
         <v>70475</v>
@@ -30709,7 +30709,7 @@
         <v>46116.34133693287</v>
       </c>
       <c r="D190" s="1">
-        <v>46116.59128472222</v>
+        <v>46116.34128472222</v>
       </c>
       <c r="E190">
         <v>70662</v>
@@ -30852,7 +30852,7 @@
         <v>46116.34157778935</v>
       </c>
       <c r="D191" s="1">
-        <v>46116.59155092593</v>
+        <v>46116.34155092593</v>
       </c>
       <c r="E191">
         <v>70972</v>
@@ -30995,7 +30995,7 @@
         <v>46116.34165016204</v>
       </c>
       <c r="D192" s="1">
-        <v>46116.591631944444</v>
+        <v>46116.341631944444</v>
       </c>
       <c r="E192">
         <v>71146</v>
@@ -31138,7 +31138,7 @@
         <v>46116.34195350695</v>
       </c>
       <c r="D193" s="1">
-        <v>46116.591898148145</v>
+        <v>46116.341898148145</v>
       </c>
       <c r="E193">
         <v>71427</v>
@@ -31281,7 +31281,7 @@
         <v>46116.34202880787</v>
       </c>
       <c r="D194" s="1">
-        <v>46116.59197916667</v>
+        <v>46116.34197916667</v>
       </c>
       <c r="E194">
         <v>71595</v>
@@ -31424,7 +31424,7 @@
         <v>46116.34227197916</v>
       </c>
       <c r="D195" s="1">
-        <v>46116.59224537037</v>
+        <v>46116.34224537037</v>
       </c>
       <c r="E195">
         <v>71904</v>
@@ -31567,7 +31567,7 @@
         <v>46116.342649212966</v>
       </c>
       <c r="D196" s="1">
-        <v>46116.59259259259</v>
+        <v>46116.34259259259</v>
       </c>
       <c r="E196">
         <v>72375</v>
@@ -31710,7 +31710,7 @@
         <v>46116.34296835648</v>
       </c>
       <c r="D197" s="1">
-        <v>46116.592939814815</v>
+        <v>46116.342939814815</v>
       </c>
       <c r="E197">
         <v>72879</v>
@@ -31853,7 +31853,7 @@
         <v>46116.34304064815</v>
       </c>
       <c r="D198" s="1">
-        <v>46116.59302083333</v>
+        <v>46116.34302083333</v>
       </c>
       <c r="E198">
         <v>73074</v>
@@ -31996,7 +31996,7 @@
         <v>46116.34334443287</v>
       </c>
       <c r="D199" s="1">
-        <v>46116.59328703704</v>
+        <v>46116.34328703704</v>
       </c>
       <c r="E199">
         <v>73444</v>
@@ -32139,7 +32139,7 @@
         <v>46116.3434190625</v>
       </c>
       <c r="D200" s="1">
-        <v>46116.59336805555</v>
+        <v>46116.34336805555</v>
       </c>
       <c r="E200">
         <v>73631</v>
@@ -32282,7 +32282,7 @@
         <v>46116.34366133102</v>
       </c>
       <c r="D201" s="1">
-        <v>46116.59363425926</v>
+        <v>46116.34363425926</v>
       </c>
       <c r="E201">
         <v>74020</v>
@@ -32425,7 +32425,7 @@
         <v>46116.3437325</v>
       </c>
       <c r="D202" s="1">
-        <v>46116.59371527778</v>
+        <v>46116.34371527778</v>
       </c>
       <c r="E202">
         <v>74208</v>
@@ -32568,7 +32568,7 @@
         <v>46116.34403710648</v>
       </c>
       <c r="D203" s="1">
-        <v>46116.593981481485</v>
+        <v>46116.343981481485</v>
       </c>
       <c r="E203">
         <v>74572</v>
@@ -32711,7 +32711,7 @@
         <v>46116.34411109953</v>
       </c>
       <c r="D204" s="1">
-        <v>46116.5940625</v>
+        <v>46116.3440625</v>
       </c>
       <c r="E204">
         <v>74749</v>
@@ -32854,7 +32854,7 @@
         <v>46116.34435555556</v>
       </c>
       <c r="D205" s="1">
-        <v>46116.5943287037</v>
+        <v>46116.3443287037</v>
       </c>
       <c r="E205">
         <v>75094</v>
@@ -32997,7 +32997,7 @@
         <v>46116.34443305556</v>
       </c>
       <c r="D206" s="1">
-        <v>46116.594409722224</v>
+        <v>46116.344409722224</v>
       </c>
       <c r="E206">
         <v>75275</v>
@@ -33140,7 +33140,7 @@
         <v>46116.34473158565</v>
       </c>
       <c r="D207" s="1">
-        <v>46116.594675925924</v>
+        <v>46116.344675925924</v>
       </c>
       <c r="E207">
         <v>75620</v>
@@ -33283,7 +33283,7 @@
         <v>46116.344802962965</v>
       </c>
       <c r="D208" s="1">
-        <v>46116.59475694445</v>
+        <v>46116.34475694445</v>
       </c>
       <c r="E208">
         <v>75803</v>
@@ -33426,7 +33426,7 @@
         <v>46116.34505011574</v>
       </c>
       <c r="D209" s="1">
-        <v>46116.59502314815</v>
+        <v>46116.34502314815</v>
       </c>
       <c r="E209">
         <v>76109</v>
@@ -33569,7 +33569,7 @@
         <v>46116.345122824074</v>
       </c>
       <c r="D210" s="1">
-        <v>46116.59510416666</v>
+        <v>46116.34510416666</v>
       </c>
       <c r="E210">
         <v>76287</v>
@@ -33712,7 +33712,7 @@
         <v>46116.34542605324</v>
       </c>
       <c r="D211" s="1">
-        <v>46116.59537037037</v>
+        <v>46116.34537037037</v>
       </c>
       <c r="E211">
         <v>76593</v>
@@ -33855,7 +33855,7 @@
         <v>46116.345503993056</v>
       </c>
       <c r="D212" s="1">
-        <v>46116.59545138889</v>
+        <v>46116.34545138889</v>
       </c>
       <c r="E212">
         <v>76760</v>
@@ -33998,7 +33998,7 @@
         <v>46116.34574471065</v>
       </c>
       <c r="D213" s="1">
-        <v>46116.595717592594</v>
+        <v>46116.345717592594</v>
       </c>
       <c r="E213">
         <v>77023</v>
@@ -34141,7 +34141,7 @@
         <v>46116.34581769676</v>
       </c>
       <c r="D214" s="1">
-        <v>46116.59579861111</v>
+        <v>46116.34579861111</v>
       </c>
       <c r="E214">
         <v>77192</v>
@@ -34284,7 +34284,7 @@
         <v>46116.34612052084</v>
       </c>
       <c r="D215" s="1">
-        <v>46116.59606481482</v>
+        <v>46116.34606481482</v>
       </c>
       <c r="E215">
         <v>77457</v>
@@ -34427,7 +34427,7 @@
         <v>46116.346192777775</v>
       </c>
       <c r="D216" s="1">
-        <v>46116.59614583333</v>
+        <v>46116.34614583333</v>
       </c>
       <c r="E216">
         <v>77622</v>
@@ -34570,7 +34570,7 @@
         <v>46116.34643900463</v>
       </c>
       <c r="D217" s="1">
-        <v>46116.59641203703</v>
+        <v>46116.34641203703</v>
       </c>
       <c r="E217">
         <v>77876</v>
@@ -34713,7 +34713,7 @@
         <v>46116.346512627315</v>
       </c>
       <c r="D218" s="1">
-        <v>46116.59649305556</v>
+        <v>46116.34649305556</v>
       </c>
       <c r="E218">
         <v>78070</v>
@@ -34856,7 +34856,7 @@
         <v>46116.34681524306</v>
       </c>
       <c r="D219" s="1">
-        <v>46116.59675925926</v>
+        <v>46116.34675925926</v>
       </c>
       <c r="E219">
         <v>78353</v>
@@ -34999,7 +34999,7 @@
         <v>46116.34689046296</v>
       </c>
       <c r="D220" s="1">
-        <v>46116.59684027778</v>
+        <v>46116.34684027778</v>
       </c>
       <c r="E220">
         <v>78536</v>
@@ -35142,7 +35142,7 @@
         <v>46116.34713364583</v>
       </c>
       <c r="D221" s="1">
-        <v>46116.59710648148</v>
+        <v>46116.34710648148</v>
       </c>
       <c r="E221">
         <v>78869</v>
@@ -35285,7 +35285,7 @@
         <v>46116.347509872685</v>
       </c>
       <c r="D222" s="1">
-        <v>46116.597453703704</v>
+        <v>46116.347453703704</v>
       </c>
       <c r="E222">
         <v>79419</v>
@@ -35428,7 +35428,7 @@
         <v>46116.34758295139</v>
       </c>
       <c r="D223" s="1">
-        <v>46116.59753472222</v>
+        <v>46116.34753472222</v>
       </c>
       <c r="E223">
         <v>79621</v>
@@ -35571,7 +35571,7 @@
         <v>46116.34782894676</v>
       </c>
       <c r="D224" s="1">
-        <v>46116.59780092593</v>
+        <v>46116.34780092593</v>
       </c>
       <c r="E224">
         <v>79965</v>
@@ -35714,7 +35714,7 @@
         <v>46116.34790386574</v>
       </c>
       <c r="D225" s="1">
-        <v>46116.59788194444</v>
+        <v>46116.34788194444</v>
       </c>
       <c r="E225">
         <v>80153</v>
@@ -35857,7 +35857,7 @@
         <v>46116.34820435185</v>
       </c>
       <c r="D226" s="1">
-        <v>46116.59814814815</v>
+        <v>46116.34814814815</v>
       </c>
       <c r="E226">
         <v>80465</v>
@@ -36000,7 +36000,7 @@
         <v>46116.34827454861</v>
       </c>
       <c r="D227" s="1">
-        <v>46116.598229166666</v>
+        <v>46116.348229166666</v>
       </c>
       <c r="E227">
         <v>80656</v>
@@ -36143,7 +36143,7 @@
         <v>46116.34852251157</v>
       </c>
       <c r="D228" s="1">
-        <v>46116.598495370374</v>
+        <v>46116.348495370374</v>
       </c>
       <c r="E228">
         <v>80943</v>
@@ -36286,7 +36286,7 @@
         <v>46116.34859585648</v>
       </c>
       <c r="D229" s="1">
-        <v>46116.59857638889</v>
+        <v>46116.34857638889</v>
       </c>
       <c r="E229">
         <v>81106</v>
@@ -36429,7 +36429,7 @@
         <v>46116.34889855324</v>
       </c>
       <c r="D230" s="1">
-        <v>46116.59884259259</v>
+        <v>46116.34884259259</v>
       </c>
       <c r="E230">
         <v>81382</v>
@@ -36572,7 +36572,7 @@
         <v>46116.34897604166</v>
       </c>
       <c r="D231" s="1">
-        <v>46116.59892361111</v>
+        <v>46116.34892361111</v>
       </c>
       <c r="E231">
         <v>81543</v>
@@ -36715,7 +36715,7 @@
         <v>46116.34921863426</v>
       </c>
       <c r="D232" s="1">
-        <v>46116.59918981481</v>
+        <v>46116.34918981481</v>
       </c>
       <c r="E232">
         <v>81796</v>
@@ -36858,7 +36858,7 @@
         <v>46116.34929111111</v>
       </c>
       <c r="D233" s="1">
-        <v>46116.599270833336</v>
+        <v>46116.349270833336</v>
       </c>
       <c r="E233">
         <v>81966</v>
@@ -37001,7 +37001,7 @@
         <v>46116.34959333333</v>
       </c>
       <c r="D234" s="1">
-        <v>46116.59953703704</v>
+        <v>46116.34953703704</v>
       </c>
       <c r="E234">
         <v>82217</v>
@@ -37144,7 +37144,7 @@
         <v>46116.349665567126</v>
       </c>
       <c r="D235" s="1">
-        <v>46116.59961805555</v>
+        <v>46116.34961805555</v>
       </c>
       <c r="E235">
         <v>82402</v>
@@ -37287,7 +37287,7 @@
         <v>46116.349911377314</v>
       </c>
       <c r="D236" s="1">
-        <v>46116.59988425926</v>
+        <v>46116.34988425926</v>
       </c>
       <c r="E236">
         <v>82717</v>
@@ -37430,7 +37430,7 @@
         <v>46116.349985787034</v>
       </c>
       <c r="D237" s="1">
-        <v>46116.599965277775</v>
+        <v>46116.349965277775</v>
       </c>
       <c r="E237">
         <v>82901</v>
@@ -37573,7 +37573,7 @@
         <v>46116.35028766204</v>
       </c>
       <c r="D238" s="1">
-        <v>46116.60023148148</v>
+        <v>46116.35023148148</v>
       </c>
       <c r="E238">
         <v>83254</v>
@@ -37716,7 +37716,7 @@
         <v>46116.35036335648</v>
       </c>
       <c r="D239" s="1">
-        <v>46116.6003125</v>
+        <v>46116.3503125</v>
       </c>
       <c r="E239">
         <v>83462</v>
@@ -37859,7 +37859,7 @@
         <v>46116.35060611111</v>
       </c>
       <c r="D240" s="1">
-        <v>46116.60057870371</v>
+        <v>46116.35057870371</v>
       </c>
       <c r="E240">
         <v>83851</v>
@@ -38002,7 +38002,7 @@
         <v>46116.35067655092</v>
       </c>
       <c r="D241" s="1">
-        <v>46116.60065972222</v>
+        <v>46116.35065972222</v>
       </c>
       <c r="E241">
         <v>84043</v>
@@ -38145,7 +38145,7 @@
         <v>46116.350982407406</v>
       </c>
       <c r="D242" s="1">
-        <v>46116.60092592592</v>
+        <v>46116.35092592592</v>
       </c>
       <c r="E242">
         <v>84416</v>
@@ -38288,7 +38288,7 @@
         <v>46116.351057025466</v>
       </c>
       <c r="D243" s="1">
-        <v>46116.601006944446</v>
+        <v>46116.351006944446</v>
       </c>
       <c r="E243">
         <v>84601</v>
@@ -38431,7 +38431,7 @@
         <v>46116.351300358794</v>
       </c>
       <c r="D244" s="1">
-        <v>46116.601273148146</v>
+        <v>46116.351273148146</v>
       </c>
       <c r="E244">
         <v>84960</v>
@@ -38574,7 +38574,7 @@
         <v>46116.351375439815</v>
       </c>
       <c r="D245" s="1">
-        <v>46116.60135416667</v>
+        <v>46116.35135416667</v>
       </c>
       <c r="E245">
         <v>85144</v>
@@ -38717,7 +38717,7 @@
         <v>46116.35175188658</v>
       </c>
       <c r="D246" s="1">
-        <v>46116.60170138889</v>
+        <v>46116.35170138889</v>
       </c>
       <c r="E246">
         <v>85647</v>
@@ -38860,7 +38860,7 @@
         <v>46116.35199498843</v>
       </c>
       <c r="D247" s="1">
-        <v>46116.60196759259</v>
+        <v>46116.35196759259</v>
       </c>
       <c r="E247">
         <v>85916</v>
@@ -39003,7 +39003,7 @@
         <v>46116.35206752315</v>
       </c>
       <c r="D248" s="1">
-        <v>46116.60204861111</v>
+        <v>46116.35204861111</v>
       </c>
       <c r="E248">
         <v>86092</v>
@@ -39146,7 +39146,7 @@
         <v>46116.35237125</v>
       </c>
       <c r="D249" s="1">
-        <v>46116.602314814816</v>
+        <v>46116.352314814816</v>
       </c>
       <c r="E249">
         <v>86360</v>
@@ -39289,7 +39289,7 @@
         <v>46116.35244982639</v>
       </c>
       <c r="D250" s="1">
-        <v>46116.60239583333</v>
+        <v>46116.35239583333</v>
       </c>
       <c r="E250">
         <v>86530</v>
@@ -39432,7 +39432,7 @@
         <v>46116.35268965278</v>
       </c>
       <c r="D251" s="1">
-        <v>46116.60266203704</v>
+        <v>46116.35266203704</v>
       </c>
       <c r="E251">
         <v>86830</v>
@@ -39575,7 +39575,7 @@
         <v>46116.352763020834</v>
       </c>
       <c r="D252" s="1">
-        <v>46116.602743055555</v>
+        <v>46116.352743055555</v>
       </c>
       <c r="E252">
         <v>86985</v>
@@ -39718,7 +39718,7 @@
         <v>46116.3530675463</v>
       </c>
       <c r="D253" s="1">
-        <v>46116.60300925926</v>
+        <v>46116.35300925926</v>
       </c>
       <c r="E253">
         <v>87261</v>
@@ -39861,7 +39861,7 @@
         <v>46116.35313898148</v>
       </c>
       <c r="D254" s="1">
-        <v>46116.60309027778</v>
+        <v>46116.35309027778</v>
       </c>
       <c r="E254">
         <v>87431</v>
@@ -40004,7 +40004,7 @@
         <v>46116.35338429398</v>
       </c>
       <c r="D255" s="1">
-        <v>46116.60335648148</v>
+        <v>46116.35335648148</v>
       </c>
       <c r="E255">
         <v>87704</v>
@@ -40147,7 +40147,7 @@
         <v>46116.35346003472</v>
       </c>
       <c r="D256" s="1">
-        <v>46116.6034375</v>
+        <v>46116.3534375</v>
       </c>
       <c r="E256">
         <v>87874</v>
@@ -40290,7 +40290,7 @@
         <v>46116.35376064815</v>
       </c>
       <c r="D257" s="1">
-        <v>46116.6037037037</v>
+        <v>46116.3537037037</v>
       </c>
       <c r="E257">
         <v>88179</v>
@@ -40433,7 +40433,7 @@
         <v>46116.35383111111</v>
       </c>
       <c r="D258" s="1">
-        <v>46116.603784722225</v>
+        <v>46116.353784722225</v>
       </c>
       <c r="E258">
         <v>88361</v>
@@ -40576,7 +40576,7 @@
         <v>46116.354078564815</v>
       </c>
       <c r="D259" s="1">
-        <v>46116.604050925926</v>
+        <v>46116.354050925926</v>
       </c>
       <c r="E259">
         <v>88698</v>
@@ -40719,7 +40719,7 @@
         <v>46116.35414978009</v>
       </c>
       <c r="D260" s="1">
-        <v>46116.60413194444</v>
+        <v>46116.35413194444</v>
       </c>
       <c r="E260">
         <v>88877</v>
@@ -40862,7 +40862,7 @@
         <v>46116.354455740744</v>
       </c>
       <c r="D261" s="1">
-        <v>46116.60439814815</v>
+        <v>46116.35439814815</v>
       </c>
       <c r="E261">
         <v>89244</v>
@@ -41005,7 +41005,7 @@
         <v>46116.35453034722</v>
       </c>
       <c r="D262" s="1">
-        <v>46116.604479166665</v>
+        <v>46116.354479166665</v>
       </c>
       <c r="E262">
         <v>89444</v>
@@ -41148,7 +41148,7 @@
         <v>46116.35477288195</v>
       </c>
       <c r="D263" s="1">
-        <v>46116.60474537037</v>
+        <v>46116.35474537037</v>
       </c>
       <c r="E263">
         <v>89802</v>
@@ -41291,7 +41291,7 @@
         <v>46116.354852094904</v>
       </c>
       <c r="D264" s="1">
-        <v>46116.60482638889</v>
+        <v>46116.35482638889</v>
       </c>
       <c r="E264">
         <v>89992</v>
@@ -41434,7 +41434,7 @@
         <v>46116.35514940972</v>
       </c>
       <c r="D265" s="1">
-        <v>46116.605092592596</v>
+        <v>46116.355092592596</v>
       </c>
       <c r="E265">
         <v>90326</v>
@@ -41577,7 +41577,7 @@
         <v>46116.35522222222</v>
       </c>
       <c r="D266" s="1">
-        <v>46116.60517361111</v>
+        <v>46116.35517361111</v>
       </c>
       <c r="E266">
         <v>90517</v>
@@ -41720,7 +41720,7 @@
         <v>46116.35549059028</v>
       </c>
       <c r="D267" s="1">
-        <v>46116.60543981481</v>
+        <v>46116.35543981481</v>
       </c>
       <c r="E267">
         <v>90855</v>
@@ -41863,7 +41863,7 @@
         <v>46116.35553947917</v>
       </c>
       <c r="D268" s="1">
-        <v>46116.605520833335</v>
+        <v>46116.355520833335</v>
       </c>
       <c r="E268">
         <v>91043</v>
@@ -42006,7 +42006,7 @@
         <v>46116.3558434375</v>
       </c>
       <c r="D269" s="1">
-        <v>46116.605787037035</v>
+        <v>46116.355787037035</v>
       </c>
       <c r="E269">
         <v>91372</v>
@@ -42149,7 +42149,7 @@
         <v>46116.355917939814</v>
       </c>
       <c r="D270" s="1">
-        <v>46116.60586805556</v>
+        <v>46116.35586805556</v>
       </c>
       <c r="E270">
         <v>91553</v>
@@ -42292,7 +42292,7 @@
         <v>46116.35616190972</v>
       </c>
       <c r="D271" s="1">
-        <v>46116.60613425926</v>
+        <v>46116.35613425926</v>
       </c>
       <c r="E271">
         <v>91854</v>
@@ -42435,7 +42435,7 @@
         <v>46116.35623118056</v>
       </c>
       <c r="D272" s="1">
-        <v>46116.60621527778</v>
+        <v>46116.35621527778</v>
       </c>
       <c r="E272">
         <v>92033</v>
@@ -42578,7 +42578,7 @@
         <v>46116.35653805555</v>
       </c>
       <c r="D273" s="1">
-        <v>46116.60648148148</v>
+        <v>46116.35648148148</v>
       </c>
       <c r="E273">
         <v>92339</v>
@@ -42721,7 +42721,7 @@
         <v>46116.35660986111</v>
       </c>
       <c r="D274" s="1">
-        <v>46116.6065625</v>
+        <v>46116.3565625</v>
       </c>
       <c r="E274">
         <v>92505</v>
@@ -42864,7 +42864,7 @@
         <v>46116.35685657407</v>
       </c>
       <c r="D275" s="1">
-        <v>46116.606828703705</v>
+        <v>46116.356828703705</v>
       </c>
       <c r="E275">
         <v>92783</v>
@@ -43007,7 +43007,7 @@
         <v>46116.35693064815</v>
       </c>
       <c r="D276" s="1">
-        <v>46116.60690972222</v>
+        <v>46116.35690972222</v>
       </c>
       <c r="E276">
         <v>92952</v>
@@ -43150,7 +43150,7 @@
         <v>46116.35723259259</v>
       </c>
       <c r="D277" s="1">
-        <v>46116.60717592593</v>
+        <v>46116.35717592593</v>
       </c>
       <c r="E277">
         <v>93205</v>
@@ -43293,7 +43293,7 @@
         <v>46116.357312210646</v>
       </c>
       <c r="D278" s="1">
-        <v>46116.607256944444</v>
+        <v>46116.357256944444</v>
       </c>
       <c r="E278">
         <v>93379</v>
@@ -43436,7 +43436,7 @@
         <v>46116.35755104166</v>
       </c>
       <c r="D279" s="1">
-        <v>46116.607523148145</v>
+        <v>46116.357523148145</v>
       </c>
       <c r="E279">
         <v>93601</v>
@@ -43579,7 +43579,7 @@
         <v>46116.35762634259</v>
       </c>
       <c r="D280" s="1">
-        <v>46116.60760416667</v>
+        <v>46116.35760416667</v>
       </c>
       <c r="E280">
         <v>93772</v>
@@ -43722,7 +43722,7 @@
         <v>46116.35792693287</v>
       </c>
       <c r="D281" s="1">
-        <v>46116.60787037037</v>
+        <v>46116.35787037037</v>
       </c>
       <c r="E281">
         <v>94007</v>
@@ -43865,7 +43865,7 @@
         <v>46116.35800256945</v>
       </c>
       <c r="D282" s="1">
-        <v>46116.60795138889</v>
+        <v>46116.35795138889</v>
       </c>
       <c r="E282">
         <v>94167</v>
@@ -44008,7 +44008,7 @@
         <v>46116.35824533565</v>
       </c>
       <c r="D283" s="1">
-        <v>46116.60821759259</v>
+        <v>46116.35821759259</v>
       </c>
       <c r="E283">
         <v>94406</v>
@@ -44151,7 +44151,7 @@
         <v>46116.358314756944</v>
       </c>
       <c r="D284" s="1">
-        <v>46116.608298611114</v>
+        <v>46116.358298611114</v>
       </c>
       <c r="E284">
         <v>94577</v>
@@ -44294,7 +44294,7 @@
         <v>46116.35862209491</v>
       </c>
       <c r="D285" s="1">
-        <v>46116.608564814815</v>
+        <v>46116.358564814815</v>
       </c>
       <c r="E285">
         <v>94837</v>
@@ -44437,7 +44437,7 @@
         <v>46116.3586921875</v>
       </c>
       <c r="D286" s="1">
-        <v>46116.60864583333</v>
+        <v>46116.35864583333</v>
       </c>
       <c r="E286">
         <v>95019</v>
@@ -44580,7 +44580,7 @@
         <v>46116.35894019676</v>
       </c>
       <c r="D287" s="1">
-        <v>46116.60891203704</v>
+        <v>46116.35891203704</v>
       </c>
       <c r="E287">
         <v>95316</v>
@@ -44723,7 +44723,7 @@
         <v>46116.359018194446</v>
       </c>
       <c r="D288" s="1">
-        <v>46116.60899305555</v>
+        <v>46116.35899305555</v>
       </c>
       <c r="E288">
         <v>95503</v>
@@ -44866,7 +44866,7 @@
         <v>46116.35931636574</v>
       </c>
       <c r="D289" s="1">
-        <v>46116.60925925926</v>
+        <v>46116.35925925926</v>
       </c>
       <c r="E289">
         <v>95825</v>
@@ -45009,7 +45009,7 @@
         <v>46116.359389826386</v>
       </c>
       <c r="D290" s="1">
-        <v>46116.60934027778</v>
+        <v>46116.35934027778</v>
       </c>
       <c r="E290">
         <v>96007</v>
@@ -45152,7 +45152,7 @@
         <v>46116.359634444445</v>
       </c>
       <c r="D291" s="1">
-        <v>46116.609606481485</v>
+        <v>46116.359606481485</v>
       </c>
       <c r="E291">
         <v>96331</v>
@@ -45295,7 +45295,7 @@
         <v>46116.35970896991</v>
       </c>
       <c r="D292" s="1">
-        <v>46116.6096875</v>
+        <v>46116.3596875</v>
       </c>
       <c r="E292">
         <v>96515</v>
@@ -45438,7 +45438,7 @@
         <v>46116.3600103125</v>
       </c>
       <c r="D293" s="1">
-        <v>46116.6099537037</v>
+        <v>46116.3599537037</v>
       </c>
       <c r="E293">
         <v>96821</v>
@@ -45581,7 +45581,7 @@
         <v>46116.36008150463</v>
       </c>
       <c r="D294" s="1">
-        <v>46116.610034722224</v>
+        <v>46116.360034722224</v>
       </c>
       <c r="E294">
         <v>97001</v>
@@ -45724,7 +45724,7 @@
         <v>46116.36034032408</v>
       </c>
       <c r="D295" s="1">
-        <v>46116.610300925924</v>
+        <v>46116.360300925924</v>
       </c>
       <c r="E295">
         <v>97272</v>
@@ -45867,7 +45867,7 @@
         <v>46116.36040133102</v>
       </c>
       <c r="D296" s="1">
-        <v>46116.61038194445</v>
+        <v>46116.36038194445</v>
       </c>
       <c r="E296">
         <v>97434</v>
@@ -46010,7 +46010,7 @@
         <v>46116.360705162035</v>
       </c>
       <c r="D297" s="1">
-        <v>46116.61064814815</v>
+        <v>46116.36064814815</v>
       </c>
       <c r="E297">
         <v>97663</v>
@@ -46153,7 +46153,7 @@
         <v>46116.36084231482</v>
       </c>
       <c r="D298" s="1">
-        <v>46116.61072916666</v>
+        <v>46116.36072916666</v>
       </c>
       <c r="E298">
         <v>97827</v>
@@ -46452,7 +46452,7 @@
         <v>46116.36102333333</v>
       </c>
       <c r="D2" s="1">
-        <v>46116.61099537037</v>
+        <v>46116.36099537037</v>
       </c>
       <c r="E2">
         <v>94777</v>
@@ -46559,7 +46559,7 @@
         <v>46116.361105104166</v>
       </c>
       <c r="D3" s="1">
-        <v>46116.61107638889</v>
+        <v>46116.36107638889</v>
       </c>
       <c r="E3">
         <v>94007</v>
@@ -46690,7 +46690,7 @@
         <v>46116.36139965278</v>
       </c>
       <c r="D4" s="1">
-        <v>46116.611342592594</v>
+        <v>46116.361342592594</v>
       </c>
       <c r="E4">
         <v>90818</v>
@@ -46833,7 +46833,7 @@
         <v>46116.36147243056</v>
       </c>
       <c r="D5" s="1">
-        <v>46116.61142361111</v>
+        <v>46116.36142361111</v>
       </c>
       <c r="E5">
         <v>90174</v>
@@ -46976,7 +46976,7 @@
         <v>46116.3617177662</v>
       </c>
       <c r="D6" s="1">
-        <v>46116.61168981482</v>
+        <v>46116.36168981482</v>
       </c>
       <c r="E6">
         <v>87276</v>
@@ -47119,7 +47119,7 @@
         <v>46116.361791331015</v>
       </c>
       <c r="D7" s="1">
-        <v>46116.61177083333</v>
+        <v>46116.36177083333</v>
       </c>
       <c r="E7">
         <v>86680</v>
@@ -47262,7 +47262,7 @@
         <v>46116.362093958334</v>
       </c>
       <c r="D8" s="1">
-        <v>46116.61203703703</v>
+        <v>46116.36203703703</v>
       </c>
       <c r="E8">
         <v>84071</v>
@@ -47405,7 +47405,7 @@
         <v>46116.36241219907</v>
       </c>
       <c r="D9" s="1">
-        <v>46116.61238425926</v>
+        <v>46116.36238425926</v>
       </c>
       <c r="E9">
         <v>81115</v>
@@ -47548,7 +47548,7 @@
         <v>46116.362483680554</v>
       </c>
       <c r="D10" s="1">
-        <v>46116.61246527778</v>
+        <v>46116.36246527778</v>
       </c>
       <c r="E10">
         <v>80599</v>
@@ -47691,7 +47691,7 @@
         <v>46116.36278859954</v>
       </c>
       <c r="D11" s="1">
-        <v>46116.61273148148</v>
+        <v>46116.36273148148</v>
       </c>
       <c r="E11">
         <v>78263</v>
@@ -47834,7 +47834,7 @@
         <v>46116.362861712965</v>
       </c>
       <c r="D12" s="1">
-        <v>46116.6128125</v>
+        <v>46116.3628125</v>
       </c>
       <c r="E12">
         <v>77767</v>
@@ -47977,7 +47977,7 @@
         <v>46116.363118333335</v>
       </c>
       <c r="D13" s="1">
-        <v>46116.613078703704</v>
+        <v>46116.363078703704</v>
       </c>
       <c r="E13">
         <v>75623</v>
@@ -48120,7 +48120,7 @@
         <v>46116.36318291667</v>
       </c>
       <c r="D14" s="1">
-        <v>46116.61315972222</v>
+        <v>46116.36315972222</v>
       </c>
       <c r="E14">
         <v>75156</v>
@@ -48263,7 +48263,7 @@
         <v>46116.36348309028</v>
       </c>
       <c r="D15" s="1">
-        <v>46116.61342592593</v>
+        <v>46116.36342592593</v>
       </c>
       <c r="E15">
         <v>73082</v>
@@ -48406,7 +48406,7 @@
         <v>46116.363558310186</v>
       </c>
       <c r="D16" s="1">
-        <v>46116.61350694444</v>
+        <v>46116.36350694444</v>
       </c>
       <c r="E16">
         <v>72658</v>
@@ -48549,7 +48549,7 @@
         <v>46116.363801377316</v>
       </c>
       <c r="D17" s="1">
-        <v>46116.61377314815</v>
+        <v>46116.36377314815</v>
       </c>
       <c r="E17">
         <v>70754</v>
@@ -48692,7 +48692,7 @@
         <v>46116.363875717594</v>
       </c>
       <c r="D18" s="1">
-        <v>46116.613854166666</v>
+        <v>46116.363854166666</v>
       </c>
       <c r="E18">
         <v>70387</v>
@@ -48835,7 +48835,7 @@
         <v>46116.364177627314</v>
       </c>
       <c r="D19" s="1">
-        <v>46116.614120370374</v>
+        <v>46116.364120370374</v>
       </c>
       <c r="E19">
         <v>68507</v>
@@ -48978,7 +48978,7 @@
         <v>46116.364248935184</v>
       </c>
       <c r="D20" s="1">
-        <v>46116.61420138889</v>
+        <v>46116.36420138889</v>
       </c>
       <c r="E20">
         <v>68135</v>
@@ -49121,7 +49121,7 @@
         <v>46116.36449559028</v>
       </c>
       <c r="D21" s="1">
-        <v>46116.61446759259</v>
+        <v>46116.36446759259</v>
       </c>
       <c r="E21">
         <v>66431</v>
@@ -49264,7 +49264,7 @@
         <v>46116.36456799768</v>
       </c>
       <c r="D22" s="1">
-        <v>46116.61454861111</v>
+        <v>46116.36454861111</v>
       </c>
       <c r="E22">
         <v>66068</v>
@@ -49407,7 +49407,7 @@
         <v>46116.36487204861</v>
       </c>
       <c r="D23" s="1">
-        <v>46116.61481481481</v>
+        <v>46116.36481481481</v>
       </c>
       <c r="E23">
         <v>64508</v>
@@ -49550,7 +49550,7 @@
         <v>46116.36501613426</v>
       </c>
       <c r="D24" s="1">
-        <v>46116.614895833336</v>
+        <v>46116.364895833336</v>
       </c>
       <c r="E24">
         <v>64213</v>
@@ -49693,7 +49693,7 @@
         <v>46116.3651903125</v>
       </c>
       <c r="D25" s="1">
-        <v>46116.61516203704</v>
+        <v>46116.36516203704</v>
       </c>
       <c r="E25">
         <v>62682</v>
@@ -49836,7 +49836,7 @@
         <v>46116.36526028935</v>
       </c>
       <c r="D26" s="1">
-        <v>46116.61524305555</v>
+        <v>46116.36524305555</v>
       </c>
       <c r="E26">
         <v>62402</v>
@@ -49979,7 +49979,7 @@
         <v>46116.365566388886</v>
       </c>
       <c r="D27" s="1">
-        <v>46116.61550925926</v>
+        <v>46116.36550925926</v>
       </c>
       <c r="E27">
         <v>60829</v>
@@ -50122,7 +50122,7 @@
         <v>46116.365636979164</v>
       </c>
       <c r="D28" s="1">
-        <v>46116.615590277775</v>
+        <v>46116.365590277775</v>
       </c>
       <c r="E28">
         <v>60539</v>
@@ -50265,7 +50265,7 @@
         <v>46116.36588486111</v>
       </c>
       <c r="D29" s="1">
-        <v>46116.61585648148</v>
+        <v>46116.36585648148</v>
       </c>
       <c r="E29">
         <v>59085</v>
@@ -50408,7 +50408,7 @@
         <v>46116.365959386574</v>
       </c>
       <c r="D30" s="1">
-        <v>46116.6159375</v>
+        <v>46116.3659375</v>
       </c>
       <c r="E30">
         <v>59062</v>
@@ -50551,7 +50551,7 @@
         <v>46116.36626322917</v>
       </c>
       <c r="D31" s="1">
-        <v>46116.61620370371</v>
+        <v>46116.36620370371</v>
       </c>
       <c r="E31">
         <v>57660</v>
@@ -50694,7 +50694,7 @@
         <v>46116.366327222226</v>
       </c>
       <c r="D32" s="1">
-        <v>46116.61628472222</v>
+        <v>46116.36628472222</v>
       </c>
       <c r="E32">
         <v>57453</v>
@@ -50837,7 +50837,7 @@
         <v>46116.366580567126</v>
       </c>
       <c r="D33" s="1">
-        <v>46116.61655092592</v>
+        <v>46116.36655092592</v>
       </c>
       <c r="E33">
         <v>56230</v>
@@ -50980,7 +50980,7 @@
         <v>46116.36665148148</v>
       </c>
       <c r="D34" s="1">
-        <v>46116.616631944446</v>
+        <v>46116.366631944446</v>
       </c>
       <c r="E34">
         <v>56022</v>
@@ -51123,7 +51123,7 @@
         <v>46116.36695550926</v>
       </c>
       <c r="D35" s="1">
-        <v>46116.616898148146</v>
+        <v>46116.366898148146</v>
       </c>
       <c r="E35">
         <v>54800</v>
@@ -51266,7 +51266,7 @@
         <v>46116.367030243055</v>
       </c>
       <c r="D36" s="1">
-        <v>46116.61697916667</v>
+        <v>46116.36697916667</v>
       </c>
       <c r="E36">
         <v>54593</v>
@@ -51409,7 +51409,7 @@
         <v>46116.36727378472</v>
       </c>
       <c r="D37" s="1">
-        <v>46116.61724537037</v>
+        <v>46116.36724537037</v>
       </c>
       <c r="E37">
         <v>53448</v>
@@ -51552,7 +51552,7 @@
         <v>46116.36734387731</v>
       </c>
       <c r="D38" s="1">
-        <v>46116.61732638889</v>
+        <v>46116.36732638889</v>
       </c>
       <c r="E38">
         <v>53244</v>
@@ -51695,7 +51695,7 @@
         <v>46116.36765021991</v>
       </c>
       <c r="D39" s="1">
-        <v>46116.61759259259</v>
+        <v>46116.36759259259</v>
       </c>
       <c r="E39">
         <v>52151</v>
@@ -51838,7 +51838,7 @@
         <v>46116.36772288194</v>
       </c>
       <c r="D40" s="1">
-        <v>46116.61767361111</v>
+        <v>46116.36767361111</v>
       </c>
       <c r="E40">
         <v>51982</v>
@@ -51981,7 +51981,7 @@
         <v>46116.3679680787</v>
       </c>
       <c r="D41" s="1">
-        <v>46116.617939814816</v>
+        <v>46116.367939814816</v>
       </c>
       <c r="E41">
         <v>50932</v>
@@ -52124,7 +52124,7 @@
         <v>46116.36804219907</v>
       </c>
       <c r="D42" s="1">
-        <v>46116.61802083333</v>
+        <v>46116.36802083333</v>
       </c>
       <c r="E42">
         <v>50742</v>
@@ -52267,7 +52267,7 @@
         <v>46116.36834512732</v>
       </c>
       <c r="D43" s="1">
-        <v>46116.61828703704</v>
+        <v>46116.36828703704</v>
       </c>
       <c r="E43">
         <v>49667</v>
@@ -52410,7 +52410,7 @@
         <v>46116.36842045139</v>
       </c>
       <c r="D44" s="1">
-        <v>46116.618368055555</v>
+        <v>46116.368368055555</v>
       </c>
       <c r="E44">
         <v>49507</v>
@@ -52553,7 +52553,7 @@
         <v>46116.36866267361</v>
       </c>
       <c r="D45" s="1">
-        <v>46116.61863425926</v>
+        <v>46116.36863425926</v>
       </c>
       <c r="E45">
         <v>48457</v>
@@ -52696,7 +52696,7 @@
         <v>46116.368733738425</v>
       </c>
       <c r="D46" s="1">
-        <v>46116.61871527778</v>
+        <v>46116.36871527778</v>
       </c>
       <c r="E46">
         <v>48294</v>
@@ -52839,7 +52839,7 @@
         <v>46116.36903909722</v>
       </c>
       <c r="D47" s="1">
-        <v>46116.61898148148</v>
+        <v>46116.36898148148</v>
       </c>
       <c r="E47">
         <v>47276</v>
@@ -52982,7 +52982,7 @@
         <v>46116.36911005787</v>
       </c>
       <c r="D48" s="1">
-        <v>46116.6190625</v>
+        <v>46116.3690625</v>
       </c>
       <c r="E48">
         <v>47130</v>
@@ -53125,7 +53125,7 @@
         <v>46116.36935724537</v>
       </c>
       <c r="D49" s="1">
-        <v>46116.6193287037</v>
+        <v>46116.3693287037</v>
       </c>
       <c r="E49">
         <v>46155</v>
@@ -53268,7 +53268,7 @@
         <v>46116.369425868055</v>
       </c>
       <c r="D50" s="1">
-        <v>46116.619409722225</v>
+        <v>46116.369409722225</v>
       </c>
       <c r="E50">
         <v>46018</v>
@@ -53411,7 +53411,7 @@
         <v>46116.369734340275</v>
       </c>
       <c r="D51" s="1">
-        <v>46116.619675925926</v>
+        <v>46116.369675925926</v>
       </c>
       <c r="E51">
         <v>45056</v>
@@ -53554,7 +53554,7 @@
         <v>46116.36980453704</v>
       </c>
       <c r="D52" s="1">
-        <v>46116.61975694444</v>
+        <v>46116.36975694444</v>
       </c>
       <c r="E52">
         <v>44914</v>
@@ -53697,7 +53697,7 @@
         <v>46116.370051736114</v>
       </c>
       <c r="D53" s="1">
-        <v>46116.62002314815</v>
+        <v>46116.37002314815</v>
       </c>
       <c r="E53">
         <v>43981</v>
@@ -53840,7 +53840,7 @@
         <v>46116.37012385417</v>
       </c>
       <c r="D54" s="1">
-        <v>46116.620104166665</v>
+        <v>46116.370104166665</v>
       </c>
       <c r="E54">
         <v>43840</v>
@@ -53983,7 +53983,7 @@
         <v>46116.37042788194</v>
       </c>
       <c r="D55" s="1">
-        <v>46116.62037037037</v>
+        <v>46116.37037037037</v>
       </c>
       <c r="E55">
         <v>42901</v>
@@ -54126,7 +54126,7 @@
         <v>46116.37049734954</v>
       </c>
       <c r="D56" s="1">
-        <v>46116.62045138889</v>
+        <v>46116.37045138889</v>
       </c>
       <c r="E56">
         <v>42754</v>
@@ -54269,7 +54269,7 @@
         <v>46116.37074806713</v>
       </c>
       <c r="D57" s="1">
-        <v>46116.620717592596</v>
+        <v>46116.370717592596</v>
       </c>
       <c r="E57">
         <v>41751</v>
@@ -54412,7 +54412,7 @@
         <v>46116.37081652778</v>
       </c>
       <c r="D58" s="1">
-        <v>46116.62079861111</v>
+        <v>46116.37079861111</v>
       </c>
       <c r="E58">
         <v>41616</v>
@@ -54555,7 +54555,7 @@
         <v>46116.37112409722</v>
       </c>
       <c r="D59" s="1">
-        <v>46116.62106481481</v>
+        <v>46116.37106481481</v>
       </c>
       <c r="E59">
         <v>40699</v>
@@ -54698,7 +54698,7 @@
         <v>46116.37118909722</v>
       </c>
       <c r="D60" s="1">
-        <v>46116.621145833335</v>
+        <v>46116.371145833335</v>
       </c>
       <c r="E60">
         <v>40581</v>
@@ -54841,7 +54841,7 @@
         <v>46116.37144221065</v>
       </c>
       <c r="D61" s="1">
-        <v>46116.621412037035</v>
+        <v>46116.371412037035</v>
       </c>
       <c r="E61">
         <v>39714</v>
@@ -54984,7 +54984,7 @@
         <v>46116.37151638889</v>
       </c>
       <c r="D62" s="1">
-        <v>46116.62149305556</v>
+        <v>46116.37149305556</v>
       </c>
       <c r="E62">
         <v>39602</v>
@@ -55127,7 +55127,7 @@
         <v>46116.37181708333</v>
       </c>
       <c r="D63" s="1">
-        <v>46116.62175925926</v>
+        <v>46116.37175925926</v>
       </c>
       <c r="E63">
         <v>38767</v>
@@ -55270,7 +55270,7 @@
         <v>46116.371880949075</v>
       </c>
       <c r="D64" s="1">
-        <v>46116.62184027778</v>
+        <v>46116.37184027778</v>
       </c>
       <c r="E64">
         <v>38664</v>
@@ -55413,7 +55413,7 @@
         <v>46116.372135578706</v>
       </c>
       <c r="D65" s="1">
-        <v>46116.62210648148</v>
+        <v>46116.37210648148</v>
       </c>
       <c r="E65">
         <v>37872</v>
@@ -55556,7 +55556,7 @@
         <v>46116.37220914352</v>
       </c>
       <c r="D66" s="1">
-        <v>46116.6221875</v>
+        <v>46116.3721875</v>
       </c>
       <c r="E66">
         <v>37785</v>
@@ -55699,7 +55699,7 @@
         <v>46116.37251302083</v>
       </c>
       <c r="D67" s="1">
-        <v>46116.622453703705</v>
+        <v>46116.372453703705</v>
       </c>
       <c r="E67">
         <v>37014</v>
@@ -55842,7 +55842,7 @@
         <v>46116.37258146991</v>
       </c>
       <c r="D68" s="1">
-        <v>46116.62253472222</v>
+        <v>46116.37253472222</v>
       </c>
       <c r="E68">
         <v>36927</v>
@@ -55985,7 +55985,7 @@
         <v>46116.372832361114</v>
       </c>
       <c r="D69" s="1">
-        <v>46116.62280092593</v>
+        <v>46116.37280092593</v>
       </c>
       <c r="E69">
         <v>36137</v>
@@ -56128,7 +56128,7 @@
         <v>46116.372897824076</v>
       </c>
       <c r="D70" s="1">
-        <v>46116.622881944444</v>
+        <v>46116.372881944444</v>
       </c>
       <c r="E70">
         <v>36044</v>
@@ -56271,7 +56271,7 @@
         <v>46116.37321989583</v>
       </c>
       <c r="D71" s="1">
-        <v>46116.623148148145</v>
+        <v>46116.373148148145</v>
       </c>
       <c r="E71">
         <v>35270</v>
@@ -56414,7 +56414,7 @@
         <v>46116.37327355324</v>
       </c>
       <c r="D72" s="1">
-        <v>46116.62322916667</v>
+        <v>46116.37322916667</v>
       </c>
       <c r="E72">
         <v>35180</v>
@@ -56557,7 +56557,7 @@
         <v>46116.37352440972</v>
       </c>
       <c r="D73" s="1">
-        <v>46116.62349537037</v>
+        <v>46116.37349537037</v>
       </c>
       <c r="E73">
         <v>34389</v>
@@ -56700,7 +56700,7 @@
         <v>46116.37359908565</v>
       </c>
       <c r="D74" s="1">
-        <v>46116.62357638889</v>
+        <v>46116.37357638889</v>
       </c>
       <c r="E74">
         <v>34303</v>
@@ -56843,7 +56843,7 @@
         <v>46116.37390348379</v>
       </c>
       <c r="D75" s="1">
-        <v>46116.62384259259</v>
+        <v>46116.37384259259</v>
       </c>
       <c r="E75">
         <v>33539</v>
@@ -56986,7 +56986,7 @@
         <v>46116.37397525463</v>
       </c>
       <c r="D76" s="1">
-        <v>46116.623923611114</v>
+        <v>46116.373923611114</v>
       </c>
       <c r="E76">
         <v>33446</v>
@@ -57129,7 +57129,7 @@
         <v>46116.37422039352</v>
       </c>
       <c r="D77" s="1">
-        <v>46116.624189814815</v>
+        <v>46116.374189814815</v>
       </c>
       <c r="E77">
         <v>32702</v>
@@ -57272,7 +57272,7 @@
         <v>46116.374287199076</v>
       </c>
       <c r="D78" s="1">
-        <v>46116.62427083333</v>
+        <v>46116.37427083333</v>
       </c>
       <c r="E78">
         <v>32624</v>
@@ -57415,7 +57415,7 @@
         <v>46116.37459037037</v>
       </c>
       <c r="D79" s="1">
-        <v>46116.62453703704</v>
+        <v>46116.37453703704</v>
       </c>
       <c r="E79">
         <v>31930</v>
@@ -57558,7 +57558,7 @@
         <v>46116.37491722222</v>
       </c>
       <c r="D80" s="1">
-        <v>46116.62488425926</v>
+        <v>46116.37488425926</v>
       </c>
       <c r="E80">
         <v>31136</v>
@@ -57701,7 +57701,7 @@
         <v>46116.37498763889</v>
       </c>
       <c r="D81" s="1">
-        <v>46116.62496527778</v>
+        <v>46116.37496527778</v>
       </c>
       <c r="E81">
         <v>31064</v>
@@ -57844,7 +57844,7 @@
         <v>46116.37528949074</v>
       </c>
       <c r="D82" s="1">
-        <v>46116.625231481485</v>
+        <v>46116.375231481485</v>
       </c>
       <c r="E82">
         <v>30380</v>
@@ -57987,7 +57987,7 @@
         <v>46116.37535715278</v>
       </c>
       <c r="D83" s="1">
-        <v>46116.6253125</v>
+        <v>46116.3753125</v>
       </c>
       <c r="E83">
         <v>30318</v>
@@ -58130,7 +58130,7 @@
         <v>46116.3756075</v>
       </c>
       <c r="D84" s="1">
-        <v>46116.6255787037</v>
+        <v>46116.3755787037</v>
       </c>
       <c r="E84">
         <v>29657</v>
@@ -58273,7 +58273,7 @@
         <v>46116.37567739583</v>
       </c>
       <c r="D85" s="1">
-        <v>46116.625659722224</v>
+        <v>46116.375659722224</v>
       </c>
       <c r="E85">
         <v>29592</v>
@@ -58416,7 +58416,7 @@
         <v>46116.375983819446</v>
       </c>
       <c r="D86" s="1">
-        <v>46116.625925925924</v>
+        <v>46116.375925925924</v>
       </c>
       <c r="E86">
         <v>28937</v>
@@ -58559,7 +58559,7 @@
         <v>46116.37605585648</v>
       </c>
       <c r="D87" s="1">
-        <v>46116.62600694445</v>
+        <v>46116.37600694445</v>
       </c>
       <c r="E87">
         <v>28871</v>
@@ -58702,7 +58702,7 @@
         <v>46116.37630224537</v>
       </c>
       <c r="D88" s="1">
-        <v>46116.62627314815</v>
+        <v>46116.37627314815</v>
       </c>
       <c r="E88">
         <v>28178</v>
@@ -58845,7 +58845,7 @@
         <v>46116.3763746412</v>
       </c>
       <c r="D89" s="1">
-        <v>46116.62635416666</v>
+        <v>46116.37635416666</v>
       </c>
       <c r="E89">
         <v>28099</v>
@@ -58988,7 +58988,7 @@
         <v>46116.37667907408</v>
       </c>
       <c r="D90" s="1">
-        <v>46116.62662037037</v>
+        <v>46116.37662037037</v>
       </c>
       <c r="E90">
         <v>27404</v>
@@ -59131,7 +59131,7 @@
         <v>46116.37675077546</v>
       </c>
       <c r="D91" s="1">
-        <v>46116.62670138889</v>
+        <v>46116.37670138889</v>
       </c>
       <c r="E91">
         <v>27337</v>
@@ -59274,7 +59274,7 @@
         <v>46116.3769909375</v>
       </c>
       <c r="D92" s="1">
-        <v>46116.626967592594</v>
+        <v>46116.376967592594</v>
       </c>
       <c r="E92">
         <v>26672</v>
@@ -59417,7 +59417,7 @@
         <v>46116.37706633102</v>
       </c>
       <c r="D93" s="1">
-        <v>46116.62704861111</v>
+        <v>46116.37704861111</v>
       </c>
       <c r="E93">
         <v>26611</v>
@@ -59560,7 +59560,7 @@
         <v>46116.37736895833</v>
       </c>
       <c r="D94" s="1">
-        <v>46116.62731481482</v>
+        <v>46116.37731481482</v>
       </c>
       <c r="E94">
         <v>25974</v>
@@ -59703,7 +59703,7 @@
         <v>46116.37744486111</v>
       </c>
       <c r="D95" s="1">
-        <v>46116.62739583333</v>
+        <v>46116.37739583333</v>
       </c>
       <c r="E95">
         <v>25919</v>
@@ -59846,7 +59846,7 @@
         <v>46116.37768680556</v>
       </c>
       <c r="D96" s="1">
-        <v>46116.62766203703</v>
+        <v>46116.37766203703</v>
       </c>
       <c r="E96">
         <v>25303</v>
@@ -59989,7 +59989,7 @@
         <v>46116.378067418984</v>
       </c>
       <c r="D97" s="1">
-        <v>46116.62800925926</v>
+        <v>46116.37800925926</v>
       </c>
       <c r="E97">
         <v>24621</v>
@@ -60132,7 +60132,7 @@
         <v>46116.378138148146</v>
       </c>
       <c r="D98" s="1">
-        <v>46116.62809027778</v>
+        <v>46116.37809027778</v>
       </c>
       <c r="E98">
         <v>24570</v>
@@ -60275,7 +60275,7 @@
         <v>46116.3783859375</v>
       </c>
       <c r="D99" s="1">
-        <v>46116.62835648148</v>
+        <v>46116.37835648148</v>
       </c>
       <c r="E99">
         <v>23960</v>
@@ -60418,7 +60418,7 @@
         <v>46116.378456770835</v>
       </c>
       <c r="D100" s="1">
-        <v>46116.6284375</v>
+        <v>46116.3784375</v>
       </c>
       <c r="E100">
         <v>23908</v>
@@ -60561,7 +60561,7 @@
         <v>46116.37876168981</v>
       </c>
       <c r="D101" s="1">
-        <v>46116.628703703704</v>
+        <v>46116.378703703704</v>
       </c>
       <c r="E101">
         <v>23298</v>
@@ -60704,7 +60704,7 @@
         <v>46116.37883884259</v>
       </c>
       <c r="D102" s="1">
-        <v>46116.62878472222</v>
+        <v>46116.37878472222</v>
       </c>
       <c r="E102">
         <v>23245</v>
@@ -60847,7 +60847,7 @@
         <v>46116.37908006945</v>
       </c>
       <c r="D103" s="1">
-        <v>46116.62905092593</v>
+        <v>46116.37905092593</v>
       </c>
       <c r="E103">
         <v>22619</v>
@@ -60990,7 +60990,7 @@
         <v>46116.37945331018</v>
       </c>
       <c r="D104" s="1">
-        <v>46116.62939814815</v>
+        <v>46116.37939814815</v>
       </c>
       <c r="E104">
         <v>21960</v>
@@ -61133,7 +61133,7 @@
         <v>46116.37953034722</v>
       </c>
       <c r="D105" s="1">
-        <v>46116.629479166666</v>
+        <v>46116.379479166666</v>
       </c>
       <c r="E105">
         <v>21911</v>
@@ -61276,7 +61276,7 @@
         <v>46116.379770659725</v>
       </c>
       <c r="D106" s="1">
-        <v>46116.629745370374</v>
+        <v>46116.379745370374</v>
       </c>
       <c r="E106">
         <v>21296</v>
@@ -61419,7 +61419,7 @@
         <v>46116.37984981482</v>
       </c>
       <c r="D107" s="1">
-        <v>46116.62982638889</v>
+        <v>46116.37982638889</v>
       </c>
       <c r="E107">
         <v>21249</v>
@@ -61562,7 +61562,7 @@
         <v>46116.380146793985</v>
       </c>
       <c r="D108" s="1">
-        <v>46116.63009259259</v>
+        <v>46116.38009259259</v>
       </c>
       <c r="E108">
         <v>20654</v>
@@ -61705,7 +61705,7 @@
         <v>46116.38022359954</v>
       </c>
       <c r="D109" s="1">
-        <v>46116.63017361111</v>
+        <v>46116.38017361111</v>
       </c>
       <c r="E109">
         <v>20605</v>
@@ -61848,7 +61848,7 @@
         <v>46116.3804690625</v>
       </c>
       <c r="D110" s="1">
-        <v>46116.63043981481</v>
+        <v>46116.38043981481</v>
       </c>
       <c r="E110">
         <v>20013</v>
@@ -61991,7 +61991,7 @@
         <v>46116.38054064815</v>
       </c>
       <c r="D111" s="1">
-        <v>46116.630520833336</v>
+        <v>46116.380520833336</v>
       </c>
       <c r="E111">
         <v>19964</v>
@@ -62134,7 +62134,7 @@
         <v>46116.38084467593</v>
       </c>
       <c r="D112" s="1">
-        <v>46116.63078703704</v>
+        <v>46116.38078703704</v>
       </c>
       <c r="E112">
         <v>19375</v>
@@ -62277,7 +62277,7 @@
         <v>46116.38092027778</v>
       </c>
       <c r="D113" s="1">
-        <v>46116.63086805555</v>
+        <v>46116.38086805555</v>
       </c>
       <c r="E113">
         <v>19324</v>
@@ -62420,7 +62420,7 @@
         <v>46116.3811599537</v>
       </c>
       <c r="D114" s="1">
-        <v>46116.63113425926</v>
+        <v>46116.38113425926</v>
       </c>
       <c r="E114">
         <v>18709</v>
@@ -62563,7 +62563,7 @@
         <v>46116.38123600694</v>
       </c>
       <c r="D115" s="1">
-        <v>46116.631215277775</v>
+        <v>46116.381215277775</v>
       </c>
       <c r="E115">
         <v>18662</v>
@@ -62706,7 +62706,7 @@
         <v>46116.38153604167</v>
       </c>
       <c r="D116" s="1">
-        <v>46116.63148148148</v>
+        <v>46116.38148148148</v>
       </c>
       <c r="E116">
         <v>18069</v>
@@ -62849,7 +62849,7 @@
         <v>46116.38160976852</v>
       </c>
       <c r="D117" s="1">
-        <v>46116.6315625</v>
+        <v>46116.3815625</v>
       </c>
       <c r="E117">
         <v>18022</v>
@@ -62992,7 +62992,7 @@
         <v>46116.38185466435</v>
       </c>
       <c r="D118" s="1">
-        <v>46116.63182870371</v>
+        <v>46116.38182870371</v>
       </c>
       <c r="E118">
         <v>17445</v>
@@ -63135,7 +63135,7 @@
         <v>46116.381928622686</v>
       </c>
       <c r="D119" s="1">
-        <v>46116.63190972222</v>
+        <v>46116.38190972222</v>
       </c>
       <c r="E119">
         <v>17401</v>
@@ -63278,7 +63278,7 @@
         <v>46116.382230208335</v>
       </c>
       <c r="D120" s="1">
-        <v>46116.63217592592</v>
+        <v>46116.38217592592</v>
       </c>
       <c r="E120">
         <v>16808</v>
@@ -63421,7 +63421,7 @@
         <v>46116.382306770836</v>
       </c>
       <c r="D121" s="1">
-        <v>46116.632256944446</v>
+        <v>46116.382256944446</v>
       </c>
       <c r="E121">
         <v>16763</v>
@@ -63564,7 +63564,7 @@
         <v>46116.38255162037</v>
       </c>
       <c r="D122" s="1">
-        <v>46116.632523148146</v>
+        <v>46116.382523148146</v>
       </c>
       <c r="E122">
         <v>16173</v>
@@ -63707,7 +63707,7 @@
         <v>46116.382620185184</v>
       </c>
       <c r="D123" s="1">
-        <v>46116.63260416667</v>
+        <v>46116.38260416667</v>
       </c>
       <c r="E123">
         <v>16133</v>
@@ -63850,7 +63850,7 @@
         <v>46116.38292524306</v>
       </c>
       <c r="D124" s="1">
-        <v>46116.63287037037</v>
+        <v>46116.38287037037</v>
       </c>
       <c r="E124">
         <v>15571</v>
@@ -63993,7 +63993,7 @@
         <v>46116.38300185185</v>
       </c>
       <c r="D125" s="1">
-        <v>46116.63295138889</v>
+        <v>46116.38295138889</v>
       </c>
       <c r="E125">
         <v>15526</v>
@@ -64136,7 +64136,7 @@
         <v>46116.38324758102</v>
       </c>
       <c r="D126" s="1">
-        <v>46116.63321759259</v>
+        <v>46116.38321759259</v>
       </c>
       <c r="E126">
         <v>14949</v>
@@ -64279,7 +64279,7 @@
         <v>46116.38332094908</v>
       </c>
       <c r="D127" s="1">
-        <v>46116.63329861111</v>
+        <v>46116.38329861111</v>
       </c>
       <c r="E127">
         <v>14901</v>
@@ -64422,7 +64422,7 @@
         <v>46116.38361898148</v>
       </c>
       <c r="D128" s="1">
-        <v>46116.633564814816</v>
+        <v>46116.383564814816</v>
       </c>
       <c r="E128">
         <v>14341</v>
@@ -64565,7 +64565,7 @@
         <v>46116.383689953705</v>
       </c>
       <c r="D129" s="1">
-        <v>46116.63364583333</v>
+        <v>46116.38364583333</v>
       </c>
       <c r="E129">
         <v>14300</v>
@@ -64708,7 +64708,7 @@
         <v>46116.38393783565</v>
       </c>
       <c r="D130" s="1">
-        <v>46116.63391203704</v>
+        <v>46116.38391203704</v>
       </c>
       <c r="E130">
         <v>13739</v>
@@ -64851,7 +64851,7 @@
         <v>46116.38401045139</v>
       </c>
       <c r="D131" s="1">
-        <v>46116.633993055555</v>
+        <v>46116.383993055555</v>
       </c>
       <c r="E131">
         <v>13702</v>
@@ -64994,7 +64994,7 @@
         <v>46116.38432466435</v>
       </c>
       <c r="D132" s="1">
-        <v>46116.63425925926</v>
+        <v>46116.38425925926</v>
       </c>
       <c r="E132">
         <v>13124</v>
@@ -65137,7 +65137,7 @@
         <v>46116.38438940972</v>
       </c>
       <c r="D133" s="1">
-        <v>46116.63434027778</v>
+        <v>46116.38434027778</v>
       </c>
       <c r="E133">
         <v>13077</v>
@@ -65280,7 +65280,7 @@
         <v>46116.384660902775</v>
       </c>
       <c r="D134" s="1">
-        <v>46116.63460648148</v>
+        <v>46116.38460648148</v>
       </c>
       <c r="E134">
         <v>12522</v>
@@ -65423,7 +65423,7 @@
         <v>46116.38471078704</v>
       </c>
       <c r="D135" s="1">
-        <v>46116.6346875</v>
+        <v>46116.3846875</v>
       </c>
       <c r="E135">
         <v>12485</v>
@@ -65566,7 +65566,7 @@
         <v>46116.38501012731</v>
       </c>
       <c r="D136" s="1">
-        <v>46116.6349537037</v>
+        <v>46116.3849537037</v>
       </c>
       <c r="E136">
         <v>11967</v>
@@ -65709,7 +65709,7 @@
         <v>46116.38533211806</v>
       </c>
       <c r="D137" s="1">
-        <v>46116.635300925926</v>
+        <v>46116.385300925926</v>
       </c>
       <c r="E137">
         <v>11418</v>
@@ -65852,7 +65852,7 @@
         <v>46116.38541284722</v>
       </c>
       <c r="D138" s="1">
-        <v>46116.63538194444</v>
+        <v>46116.38538194444</v>
       </c>
       <c r="E138">
         <v>11386</v>
@@ -65995,7 +65995,7 @@
         <v>46116.38571425926</v>
       </c>
       <c r="D139" s="1">
-        <v>46116.63564814815</v>
+        <v>46116.38564814815</v>
       </c>
       <c r="E139">
         <v>10858</v>
@@ -66138,7 +66138,7 @@
         <v>46116.38578376157</v>
       </c>
       <c r="D140" s="1">
-        <v>46116.635729166665</v>
+        <v>46116.385729166665</v>
       </c>
       <c r="E140">
         <v>10815</v>
@@ -66281,7 +66281,7 @@
         <v>46116.3860271875</v>
       </c>
       <c r="D141" s="1">
-        <v>46116.63599537037</v>
+        <v>46116.38599537037</v>
       </c>
       <c r="E141">
         <v>10259</v>
@@ -66424,7 +66424,7 @@
         <v>46116.38609664352</v>
       </c>
       <c r="D142" s="1">
-        <v>46116.63607638889</v>
+        <v>46116.38607638889</v>
       </c>
       <c r="E142">
         <v>10219</v>
@@ -66567,7 +66567,7 @@
         <v>46116.38641</v>
       </c>
       <c r="D143" s="1">
-        <v>46116.636342592596</v>
+        <v>46116.386342592596</v>
       </c>
       <c r="E143">
         <v>9658</v>
@@ -66710,7 +66710,7 @@
         <v>46116.38647932871</v>
       </c>
       <c r="D144" s="1">
-        <v>46116.63642361111</v>
+        <v>46116.38642361111</v>
       </c>
       <c r="E144">
         <v>9627</v>
@@ -66853,7 +66853,7 @@
         <v>46116.386721793984</v>
       </c>
       <c r="D145" s="1">
-        <v>46116.63668981481</v>
+        <v>46116.38668981481</v>
       </c>
       <c r="E145">
         <v>9106</v>
@@ -66996,7 +66996,7 @@
         <v>46116.38679094907</v>
       </c>
       <c r="D146" s="1">
-        <v>46116.636770833335</v>
+        <v>46116.386770833335</v>
       </c>
       <c r="E146">
         <v>9077</v>
@@ -67139,7 +67139,7 @@
         <v>46116.38710392361</v>
       </c>
       <c r="D147" s="1">
-        <v>46116.637037037035</v>
+        <v>46116.387037037035</v>
       </c>
       <c r="E147">
         <v>8545</v>
@@ -67282,7 +67282,7 @@
         <v>46116.38741701389</v>
       </c>
       <c r="D148" s="1">
-        <v>46116.63738425926</v>
+        <v>46116.38738425926</v>
       </c>
       <c r="E148">
         <v>7918</v>
@@ -67425,7 +67425,7 @@
         <v>46116.387486377316</v>
       </c>
       <c r="D149" s="1">
-        <v>46116.63746527778</v>
+        <v>46116.38746527778</v>
       </c>
       <c r="E149">
         <v>7880</v>
@@ -67568,7 +67568,7 @@
         <v>46116.38778697917</v>
       </c>
       <c r="D150" s="1">
-        <v>46116.63773148148</v>
+        <v>46116.38773148148</v>
       </c>
       <c r="E150">
         <v>7356</v>
@@ -67711,7 +67711,7 @@
         <v>46116.387868854166</v>
       </c>
       <c r="D151" s="1">
-        <v>46116.6378125</v>
+        <v>46116.3878125</v>
       </c>
       <c r="E151">
         <v>7330</v>
@@ -67854,7 +67854,7 @@
         <v>46116.38811179398</v>
       </c>
       <c r="D152" s="1">
-        <v>46116.638078703705</v>
+        <v>46116.388078703705</v>
       </c>
       <c r="E152">
         <v>6831</v>
@@ -67997,7 +67997,7 @@
         <v>46116.38849402778</v>
       </c>
       <c r="D153" s="1">
-        <v>46116.63842592593</v>
+        <v>46116.38842592593</v>
       </c>
       <c r="E153">
         <v>6338</v>
@@ -68140,7 +68140,7 @@
         <v>46116.38856319444</v>
       </c>
       <c r="D154" s="1">
-        <v>46116.638506944444</v>
+        <v>46116.388506944444</v>
       </c>
       <c r="E154">
         <v>6337</v>
@@ -68283,7 +68283,7 @@
         <v>46116.388806284725</v>
       </c>
       <c r="D155" s="1">
-        <v>46116.638773148145</v>
+        <v>46116.388773148145</v>
       </c>
       <c r="E155">
         <v>6014</v>
@@ -68426,7 +68426,7 @@
         <v>46116.388876006946</v>
       </c>
       <c r="D156" s="1">
-        <v>46116.63885416667</v>
+        <v>46116.38885416667</v>
       </c>
       <c r="E156">
         <v>6036</v>
@@ -68569,7 +68569,7 @@
         <v>46116.38917704861</v>
       </c>
       <c r="D157" s="1">
-        <v>46116.63912037037</v>
+        <v>46116.38912037037</v>
       </c>
       <c r="E157">
         <v>5688</v>
@@ -68712,7 +68712,7 @@
         <v>46116.38925782408</v>
       </c>
       <c r="D158" s="1">
-        <v>46116.63920138889</v>
+        <v>46116.38920138889</v>
       </c>
       <c r="E158">
         <v>5685</v>
@@ -68855,7 +68855,7 @@
         <v>46116.389571099535</v>
       </c>
       <c r="D159" s="1">
-        <v>46116.639548611114</v>
+        <v>46116.389548611114</v>
       </c>
       <c r="E159">
         <v>5307</v>
@@ -68998,7 +68998,7 @@
         <v>46116.391585729165</v>
       </c>
       <c r="D160" s="1">
-        <v>46116.641550925924</v>
+        <v>46116.391550925924</v>
       </c>
       <c r="E160">
         <v>4885</v>
